--- a/data/kamper_2026.xlsx
+++ b/data/kamper_2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="356">
   <si>
     <t>Runde</t>
   </si>
@@ -236,6 +236,12 @@
     <t>99120001011</t>
   </si>
   <si>
+    <t>Jotun Arena</t>
+  </si>
+  <si>
+    <t>99120001014</t>
+  </si>
+  <si>
     <t>1 - 2</t>
   </si>
   <si>
@@ -245,342 +251,336 @@
     <t>99120001010</t>
   </si>
   <si>
-    <t>Jotun Arena</t>
-  </si>
-  <si>
-    <t>99120001014</t>
-  </si>
-  <si>
     <t>Åråsen stadion</t>
   </si>
   <si>
     <t>99120001012</t>
   </si>
   <si>
+    <t>3 - 0</t>
+  </si>
+  <si>
+    <t>Aspmyra stadion</t>
+  </si>
+  <si>
+    <t>99120001009</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>mandag</t>
+  </si>
+  <si>
+    <t>0 - 1</t>
+  </si>
+  <si>
+    <t>99120001023</t>
+  </si>
+  <si>
+    <t>0 - 3</t>
+  </si>
+  <si>
+    <t>99120001019</t>
+  </si>
+  <si>
+    <t>99120001021</t>
+  </si>
+  <si>
+    <t>1 - 5</t>
+  </si>
+  <si>
+    <t>99120001017</t>
+  </si>
+  <si>
+    <t>99120001020</t>
+  </si>
+  <si>
+    <t>99120001022</t>
+  </si>
+  <si>
+    <t>tirsdag</t>
+  </si>
+  <si>
+    <t>99120001018</t>
+  </si>
+  <si>
+    <t>2 - 3</t>
+  </si>
+  <si>
+    <t>99120001024</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>99120001027</t>
+  </si>
+  <si>
+    <t>99120001030</t>
+  </si>
+  <si>
+    <t>5 - 0</t>
+  </si>
+  <si>
+    <t>99120001031</t>
+  </si>
+  <si>
+    <t>99120001029</t>
+  </si>
+  <si>
+    <t>99120001028</t>
+  </si>
+  <si>
+    <t>99120001026</t>
+  </si>
+  <si>
+    <t>2 - 2</t>
+  </si>
+  <si>
+    <t>99120001032</t>
+  </si>
+  <si>
+    <t>99120001025</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>99120001033</t>
+  </si>
+  <si>
+    <t>0 - 0</t>
+  </si>
+  <si>
+    <t>99120001036</t>
+  </si>
+  <si>
+    <t>99120001039</t>
+  </si>
+  <si>
+    <t>99120001040</t>
+  </si>
+  <si>
+    <t>99120001037</t>
+  </si>
+  <si>
+    <t>99120001034</t>
+  </si>
+  <si>
+    <t>99120001035</t>
+  </si>
+  <si>
+    <t>99120001038</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>99120001041</t>
+  </si>
+  <si>
+    <t>99120001046</t>
+  </si>
+  <si>
+    <t>5 - 1</t>
+  </si>
+  <si>
+    <t>99120001045</t>
+  </si>
+  <si>
+    <t>99120001047</t>
+  </si>
+  <si>
+    <t>99120001048</t>
+  </si>
+  <si>
+    <t>99120001042</t>
+  </si>
+  <si>
+    <t>99120001043</t>
+  </si>
+  <si>
+    <t>99120001044</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>fredag</t>
+  </si>
+  <si>
+    <t>99120001055</t>
+  </si>
+  <si>
+    <t>99120001050</t>
+  </si>
+  <si>
+    <t>99120001052</t>
+  </si>
+  <si>
+    <t>99120001051</t>
+  </si>
+  <si>
+    <t>99120001053</t>
+  </si>
+  <si>
+    <t>99120001054</t>
+  </si>
+  <si>
+    <t>99120001056</t>
+  </si>
+  <si>
+    <t>99120001049</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>99120001057</t>
+  </si>
+  <si>
+    <t>99120001061</t>
+  </si>
+  <si>
+    <t>99120001059</t>
+  </si>
+  <si>
+    <t>99120001060</t>
+  </si>
+  <si>
+    <t>99120001063</t>
+  </si>
+  <si>
+    <t>99120001058</t>
+  </si>
+  <si>
+    <t>1 - 4</t>
+  </si>
+  <si>
+    <t>99120001062</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>99120001064</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>99120001066</t>
+  </si>
+  <si>
+    <t>99120001068</t>
+  </si>
+  <si>
+    <t>99120001070</t>
+  </si>
+  <si>
+    <t>99120001067</t>
+  </si>
+  <si>
+    <t>6 - 3</t>
+  </si>
+  <si>
+    <t>99120001071</t>
+  </si>
+  <si>
+    <t>99120001069</t>
+  </si>
+  <si>
+    <t>99120001065</t>
+  </si>
+  <si>
+    <t>99120001072</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>99120001073</t>
+  </si>
+  <si>
+    <t>99120001076</t>
+  </si>
+  <si>
+    <t>99120001079</t>
+  </si>
+  <si>
+    <t>99120001074</t>
+  </si>
+  <si>
+    <t>99120001075</t>
+  </si>
+  <si>
+    <t>99120001080</t>
+  </si>
+  <si>
+    <t>99120001078</t>
+  </si>
+  <si>
+    <t>99120001077</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>99120001081</t>
+  </si>
+  <si>
+    <t>99120001087</t>
+  </si>
+  <si>
+    <t>99120001082</t>
+  </si>
+  <si>
+    <t>99120001083</t>
+  </si>
+  <si>
+    <t>99120001086</t>
+  </si>
+  <si>
+    <t>99120001088</t>
+  </si>
+  <si>
+    <t>99120001085</t>
+  </si>
+  <si>
+    <t>99120001084</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Aspmyra stadion</t>
-  </si>
-  <si>
-    <t>99120001009</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>mandag</t>
-  </si>
-  <si>
-    <t>0 - 1</t>
-  </si>
-  <si>
-    <t>99120001023</t>
-  </si>
-  <si>
-    <t>0 - 3</t>
-  </si>
-  <si>
-    <t>99120001019</t>
-  </si>
-  <si>
-    <t>99120001021</t>
-  </si>
-  <si>
-    <t>1 - 5</t>
-  </si>
-  <si>
-    <t>99120001017</t>
-  </si>
-  <si>
-    <t>99120001020</t>
-  </si>
-  <si>
-    <t>99120001022</t>
-  </si>
-  <si>
-    <t>tirsdag</t>
-  </si>
-  <si>
-    <t>99120001018</t>
-  </si>
-  <si>
-    <t>2 - 3</t>
-  </si>
-  <si>
-    <t>99120001024</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>99120001027</t>
-  </si>
-  <si>
-    <t>99120001030</t>
-  </si>
-  <si>
-    <t>5 - 0</t>
-  </si>
-  <si>
-    <t>99120001031</t>
-  </si>
-  <si>
-    <t>99120001029</t>
-  </si>
-  <si>
-    <t>99120001028</t>
-  </si>
-  <si>
-    <t>99120001026</t>
-  </si>
-  <si>
-    <t>2 - 2</t>
-  </si>
-  <si>
-    <t>99120001032</t>
-  </si>
-  <si>
-    <t>99120001025</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>3 - 0</t>
-  </si>
-  <si>
-    <t>99120001033</t>
-  </si>
-  <si>
-    <t>0 - 0</t>
-  </si>
-  <si>
-    <t>99120001036</t>
-  </si>
-  <si>
-    <t>99120001039</t>
-  </si>
-  <si>
-    <t>99120001040</t>
-  </si>
-  <si>
-    <t>99120001037</t>
-  </si>
-  <si>
-    <t>99120001034</t>
-  </si>
-  <si>
-    <t>99120001035</t>
-  </si>
-  <si>
-    <t>99120001038</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>99120001041</t>
-  </si>
-  <si>
-    <t>99120001046</t>
-  </si>
-  <si>
-    <t>5 - 1</t>
-  </si>
-  <si>
-    <t>99120001045</t>
-  </si>
-  <si>
-    <t>99120001047</t>
-  </si>
-  <si>
-    <t>99120001048</t>
-  </si>
-  <si>
-    <t>99120001042</t>
-  </si>
-  <si>
-    <t>99120001043</t>
-  </si>
-  <si>
-    <t>99120001044</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>fredag</t>
-  </si>
-  <si>
-    <t>99120001055</t>
-  </si>
-  <si>
-    <t>99120001050</t>
-  </si>
-  <si>
-    <t>99120001052</t>
-  </si>
-  <si>
-    <t>99120001051</t>
-  </si>
-  <si>
-    <t>99120001053</t>
-  </si>
-  <si>
-    <t>99120001054</t>
-  </si>
-  <si>
-    <t>99120001056</t>
-  </si>
-  <si>
-    <t>99120001049</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>99120001057</t>
-  </si>
-  <si>
-    <t>99120001061</t>
-  </si>
-  <si>
-    <t>99120001059</t>
-  </si>
-  <si>
-    <t>99120001060</t>
-  </si>
-  <si>
-    <t>99120001063</t>
-  </si>
-  <si>
-    <t>99120001058</t>
-  </si>
-  <si>
-    <t>1 - 4</t>
-  </si>
-  <si>
-    <t>99120001062</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>99120001064</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>99120001066</t>
-  </si>
-  <si>
-    <t>99120001068</t>
-  </si>
-  <si>
-    <t>99120001070</t>
-  </si>
-  <si>
-    <t>99120001067</t>
-  </si>
-  <si>
-    <t>99120001069</t>
-  </si>
-  <si>
-    <t>6 - 3</t>
-  </si>
-  <si>
-    <t>99120001071</t>
-  </si>
-  <si>
-    <t>99120001065</t>
-  </si>
-  <si>
-    <t>99120001072</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>99120001073</t>
-  </si>
-  <si>
-    <t>99120001076</t>
-  </si>
-  <si>
-    <t>99120001079</t>
-  </si>
-  <si>
-    <t>99120001074</t>
-  </si>
-  <si>
-    <t>99120001075</t>
-  </si>
-  <si>
-    <t>99120001078</t>
-  </si>
-  <si>
-    <t>99120001080</t>
-  </si>
-  <si>
-    <t>99120001077</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>99120001081</t>
-  </si>
-  <si>
-    <t>99120001087</t>
-  </si>
-  <si>
-    <t>99120001082</t>
-  </si>
-  <si>
-    <t>99120001083</t>
-  </si>
-  <si>
-    <t>99120001086</t>
-  </si>
-  <si>
-    <t>99120001088</t>
-  </si>
-  <si>
-    <t>99120001085</t>
-  </si>
-  <si>
-    <t>99120001084</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>99120001091</t>
   </si>
   <si>
     <t>99120001092</t>
   </si>
   <si>
+    <t>99120001095</t>
+  </si>
+  <si>
     <t>99120001096</t>
   </si>
   <si>
-    <t>99120001095</t>
-  </si>
-  <si>
     <t>99120001089</t>
   </si>
   <si>
+    <t>99120001090</t>
+  </si>
+  <si>
     <t>99120001093</t>
   </si>
   <si>
-    <t>99120001090</t>
-  </si>
-  <si>
     <t>99120001094</t>
   </si>
   <si>
@@ -617,6 +617,9 @@
     <t>torsdag</t>
   </si>
   <si>
+    <t>6 - 1</t>
+  </si>
+  <si>
     <t>99120001112</t>
   </si>
   <si>
@@ -653,15 +656,15 @@
     <t>99120001113</t>
   </si>
   <si>
+    <t>99120001117</t>
+  </si>
+  <si>
+    <t>99120001118</t>
+  </si>
+  <si>
     <t>99120001114</t>
   </si>
   <si>
-    <t>99120001117</t>
-  </si>
-  <si>
-    <t>99120001118</t>
-  </si>
-  <si>
     <t>99120001120</t>
   </si>
   <si>
@@ -788,6 +791,9 @@
     <t>99120001154</t>
   </si>
   <si>
+    <t>99120001160</t>
+  </si>
+  <si>
     <t>99120001158</t>
   </si>
   <si>
@@ -797,9 +803,6 @@
     <t>99120001153</t>
   </si>
   <si>
-    <t>99120001160</t>
-  </si>
-  <si>
     <t>99120001156</t>
   </si>
   <si>
@@ -866,24 +869,24 @@
     <t>23</t>
   </si>
   <si>
+    <t>99120001180</t>
+  </si>
+  <si>
     <t>99120001181</t>
   </si>
   <si>
-    <t>99120001180</t>
+    <t>99120001177</t>
   </si>
   <si>
     <t>99120001178</t>
   </si>
   <si>
+    <t>99120001179</t>
+  </si>
+  <si>
     <t>99120001182</t>
   </si>
   <si>
-    <t>99120001177</t>
-  </si>
-  <si>
-    <t>99120001179</t>
-  </si>
-  <si>
     <t>99120001183</t>
   </si>
   <si>
@@ -905,42 +908,42 @@
     <t>99120001185</t>
   </si>
   <si>
+    <t>99120001187</t>
+  </si>
+  <si>
+    <t>99120001188</t>
+  </si>
+  <si>
     <t>99120001190</t>
   </si>
   <si>
-    <t>99120001187</t>
-  </si>
-  <si>
-    <t>99120001188</t>
-  </si>
-  <si>
     <t>99120001191</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
+    <t>99120001197</t>
+  </si>
+  <si>
     <t>99120001199</t>
   </si>
   <si>
-    <t>99120001197</t>
+    <t>99120001193</t>
   </si>
   <si>
     <t>99120001194</t>
   </si>
   <si>
+    <t>99120001195</t>
+  </si>
+  <si>
     <t>99120001196</t>
   </si>
   <si>
     <t>99120001198</t>
   </si>
   <si>
-    <t>99120001193</t>
-  </si>
-  <si>
-    <t>99120001195</t>
-  </si>
-  <si>
     <t>99120001200</t>
   </si>
   <si>
@@ -986,18 +989,18 @@
     <t>99120001214</t>
   </si>
   <si>
+    <t>99120001210</t>
+  </si>
+  <si>
+    <t>99120001212</t>
+  </si>
+  <si>
+    <t>99120001215</t>
+  </si>
+  <si>
     <t>99120001216</t>
   </si>
   <si>
-    <t>99120001210</t>
-  </si>
-  <si>
-    <t>99120001212</t>
-  </si>
-  <si>
-    <t>99120001215</t>
-  </si>
-  <si>
     <t>28</t>
   </si>
   <si>
@@ -1034,6 +1037,12 @@
     <t>99120001225</t>
   </si>
   <si>
+    <t>99120001226</t>
+  </si>
+  <si>
+    <t>99120001227</t>
+  </si>
+  <si>
     <t>99120001228</t>
   </si>
   <si>
@@ -1046,15 +1055,15 @@
     <t>99120001231</t>
   </si>
   <si>
-    <t>99120001226</t>
-  </si>
-  <si>
-    <t>99120001227</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
+    <t>99120001233</t>
+  </si>
+  <si>
+    <t>99120001235</t>
+  </si>
+  <si>
     <t>99120001237</t>
   </si>
   <si>
@@ -1062,12 +1071,6 @@
   </si>
   <si>
     <t>99120001240</t>
-  </si>
-  <si>
-    <t>99120001233</t>
-  </si>
-  <si>
-    <t>99120001235</t>
   </si>
   <si>
     <t>99120001234</t>
@@ -1627,22 +1630,22 @@
         <v>34</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F14" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="0" t="s">
+      <c r="I14" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="0" t="s">
         <v>75</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="0" t="s">
-        <v>76</v>
       </c>
       <c r="K14" s="0" t="s">
         <v>20</v>
@@ -1662,13 +1665,13 @@
         <v>34</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H15" s="0" t="s">
         <v>77</v>
@@ -1700,7 +1703,7 @@
         <v>46</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>29</v>
@@ -1980,7 +1983,7 @@
         <v>35</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>41</v>
@@ -2301,7 +2304,7 @@
         <v>41</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>18</v>
@@ -2330,7 +2333,7 @@
         <v>59</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>44</v>
@@ -2342,7 +2345,7 @@
         <v>18</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K34" s="0" t="s">
         <v>20</v>
@@ -2365,19 +2368,19 @@
         <v>41</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I35" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J35" s="0" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K35" s="0" t="s">
         <v>20</v>
@@ -2412,7 +2415,7 @@
         <v>18</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K36" s="0" t="s">
         <v>20</v>
@@ -2447,7 +2450,7 @@
         <v>18</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K37" s="0" t="s">
         <v>20</v>
@@ -2482,7 +2485,7 @@
         <v>18</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K38" s="0" t="s">
         <v>20</v>
@@ -2517,7 +2520,7 @@
         <v>18</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K39" s="0" t="s">
         <v>20</v>
@@ -2552,7 +2555,7 @@
         <v>18</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K40" s="0" t="s">
         <v>20</v>
@@ -2587,7 +2590,7 @@
         <v>18</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K41" s="0" t="s">
         <v>20</v>
@@ -2595,7 +2598,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B42" s="2">
         <v>46137.666666666664</v>
@@ -2610,7 +2613,7 @@
         <v>52</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>16</v>
@@ -2622,7 +2625,7 @@
         <v>18</v>
       </c>
       <c r="J42" s="0" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K42" s="0" t="s">
         <v>20</v>
@@ -2630,7 +2633,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B43" s="2">
         <v>46137.75</v>
@@ -2657,7 +2660,7 @@
         <v>18</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K43" s="0" t="s">
         <v>20</v>
@@ -2665,7 +2668,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B44" s="2">
         <v>46138.604166666664</v>
@@ -2680,7 +2683,7 @@
         <v>22</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>39</v>
@@ -2692,7 +2695,7 @@
         <v>18</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K44" s="0" t="s">
         <v>20</v>
@@ -2700,7 +2703,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B45" s="2">
         <v>46138.708333333336</v>
@@ -2727,7 +2730,7 @@
         <v>18</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K45" s="0" t="s">
         <v>20</v>
@@ -2735,7 +2738,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B46" s="2">
         <v>46138.708333333336</v>
@@ -2762,7 +2765,7 @@
         <v>18</v>
       </c>
       <c r="J46" s="0" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K46" s="0" t="s">
         <v>20</v>
@@ -2770,7 +2773,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B47" s="2">
         <v>46138.708333333336</v>
@@ -2797,7 +2800,7 @@
         <v>18</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K47" s="0" t="s">
         <v>20</v>
@@ -2805,7 +2808,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B48" s="2">
         <v>46138.708333333336</v>
@@ -2832,7 +2835,7 @@
         <v>18</v>
       </c>
       <c r="J48" s="0" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K48" s="0" t="s">
         <v>20</v>
@@ -2840,7 +2843,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B49" s="2">
         <v>46138.802083333336</v>
@@ -2867,7 +2870,7 @@
         <v>18</v>
       </c>
       <c r="J49" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K49" s="0" t="s">
         <v>20</v>
@@ -2875,13 +2878,13 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B50" s="2">
         <v>46143.75</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>21</v>
@@ -2890,7 +2893,7 @@
         <v>16</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>24</v>
@@ -2902,7 +2905,7 @@
         <v>18</v>
       </c>
       <c r="J50" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K50" s="0" t="s">
         <v>20</v>
@@ -2910,7 +2913,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B51" s="2">
         <v>46144.75</v>
@@ -2931,13 +2934,13 @@
         <v>52</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I51" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J51" s="0" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K51" s="0" t="s">
         <v>20</v>
@@ -2945,7 +2948,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B52" s="2">
         <v>46145.604166666664</v>
@@ -2972,7 +2975,7 @@
         <v>18</v>
       </c>
       <c r="J52" s="0" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K52" s="0" t="s">
         <v>20</v>
@@ -2980,7 +2983,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B53" s="2">
         <v>46145.708333333336</v>
@@ -3007,7 +3010,7 @@
         <v>18</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K53" s="0" t="s">
         <v>20</v>
@@ -3015,7 +3018,7 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B54" s="2">
         <v>46145.708333333336</v>
@@ -3036,13 +3039,13 @@
         <v>44</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I54" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J54" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K54" s="0" t="s">
         <v>20</v>
@@ -3050,7 +3053,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B55" s="2">
         <v>46145.708333333336</v>
@@ -3077,7 +3080,7 @@
         <v>18</v>
       </c>
       <c r="J55" s="0" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K55" s="0" t="s">
         <v>20</v>
@@ -3085,7 +3088,7 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B56" s="2">
         <v>46145.802083333336</v>
@@ -3112,7 +3115,7 @@
         <v>18</v>
       </c>
       <c r="J56" s="0" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K56" s="0" t="s">
         <v>20</v>
@@ -3120,7 +3123,7 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B57" s="2">
         <v>46146.791666666664</v>
@@ -3147,7 +3150,7 @@
         <v>18</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K57" s="0" t="s">
         <v>20</v>
@@ -3155,13 +3158,13 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B58" s="2">
         <v>46150.791666666664</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>56</v>
@@ -3182,7 +3185,7 @@
         <v>18</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K58" s="0" t="s">
         <v>20</v>
@@ -3190,7 +3193,7 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B59" s="2">
         <v>46151.583333333336</v>
@@ -3217,7 +3220,7 @@
         <v>18</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K59" s="0" t="s">
         <v>20</v>
@@ -3225,7 +3228,7 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B60" s="2">
         <v>46152.604166666664</v>
@@ -3252,7 +3255,7 @@
         <v>18</v>
       </c>
       <c r="J60" s="0" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K60" s="0" t="s">
         <v>20</v>
@@ -3260,7 +3263,7 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B61" s="2">
         <v>46152.708333333336</v>
@@ -3281,13 +3284,13 @@
         <v>29</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I61" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J61" s="0" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K61" s="0" t="s">
         <v>20</v>
@@ -3295,7 +3298,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B62" s="2">
         <v>46152.708333333336</v>
@@ -3322,7 +3325,7 @@
         <v>18</v>
       </c>
       <c r="J62" s="0" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K62" s="0" t="s">
         <v>20</v>
@@ -3330,7 +3333,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B63" s="2">
         <v>46152.708333333336</v>
@@ -3357,7 +3360,7 @@
         <v>18</v>
       </c>
       <c r="J63" s="0" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K63" s="0" t="s">
         <v>20</v>
@@ -3365,7 +3368,7 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B64" s="2">
         <v>46162.75</v>
@@ -3380,7 +3383,7 @@
         <v>36</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>59</v>
@@ -3392,7 +3395,7 @@
         <v>18</v>
       </c>
       <c r="J64" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K64" s="0" t="s">
         <v>20</v>
@@ -3400,7 +3403,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B65" s="2">
         <v>46162.833333333336</v>
@@ -3409,7 +3412,7 @@
         <v>55</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E65" s="0" t="s">
         <v>44</v>
@@ -3427,7 +3430,7 @@
         <v>18</v>
       </c>
       <c r="J65" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K65" s="0" t="s">
         <v>20</v>
@@ -3435,7 +3438,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B66" s="2">
         <v>46158.583333333336</v>
@@ -3456,13 +3459,13 @@
         <v>35</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I66" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J66" s="0" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K66" s="0" t="s">
         <v>20</v>
@@ -3470,7 +3473,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B67" s="2">
         <v>46158.666666666664</v>
@@ -3497,7 +3500,7 @@
         <v>18</v>
       </c>
       <c r="J67" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K67" s="0" t="s">
         <v>20</v>
@@ -3505,7 +3508,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B68" s="2">
         <v>46158.666666666664</v>
@@ -3532,7 +3535,7 @@
         <v>18</v>
       </c>
       <c r="J68" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K68" s="0" t="s">
         <v>20</v>
@@ -3540,7 +3543,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B69" s="2">
         <v>46158.666666666664</v>
@@ -3567,7 +3570,7 @@
         <v>18</v>
       </c>
       <c r="J69" s="0" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K69" s="0" t="s">
         <v>20</v>
@@ -3575,7 +3578,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B70" s="2">
         <v>46158.666666666664</v>
@@ -3587,16 +3590,16 @@
         <v>13</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>40</v>
+        <v>157</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="I70" s="0" t="s">
         <v>18</v>
@@ -3610,7 +3613,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B71" s="2">
         <v>46158.666666666664</v>
@@ -3622,22 +3625,22 @@
         <v>13</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F71" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="I71" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="0" t="s">
         <v>159</v>
-      </c>
-      <c r="G71" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H71" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="I71" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="0" t="s">
-        <v>160</v>
       </c>
       <c r="K71" s="0" t="s">
         <v>20</v>
@@ -3645,7 +3648,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B72" s="2">
         <v>46158.75</v>
@@ -3672,7 +3675,7 @@
         <v>18</v>
       </c>
       <c r="J72" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K72" s="0" t="s">
         <v>20</v>
@@ -3680,7 +3683,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B73" s="2">
         <v>46158.833333333336</v>
@@ -3689,7 +3692,7 @@
         <v>12</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E73" s="0" t="s">
         <v>39</v>
@@ -3707,7 +3710,7 @@
         <v>18</v>
       </c>
       <c r="J73" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K73" s="0" t="s">
         <v>20</v>
@@ -3715,7 +3718,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B74" s="2">
         <v>46166.666666666664</v>
@@ -3742,7 +3745,7 @@
         <v>18</v>
       </c>
       <c r="J74" s="0" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K74" s="0" t="s">
         <v>20</v>
@@ -3750,7 +3753,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B75" s="2">
         <v>46166.75</v>
@@ -3765,7 +3768,7 @@
         <v>29</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>16</v>
@@ -3777,7 +3780,7 @@
         <v>18</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K75" s="0" t="s">
         <v>20</v>
@@ -3785,7 +3788,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B76" s="2">
         <v>46167.604166666664</v>
@@ -3812,7 +3815,7 @@
         <v>18</v>
       </c>
       <c r="J76" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K76" s="0" t="s">
         <v>20</v>
@@ -3820,7 +3823,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B77" s="2">
         <v>46167.708333333336</v>
@@ -3847,7 +3850,7 @@
         <v>18</v>
       </c>
       <c r="J77" s="0" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K77" s="0" t="s">
         <v>20</v>
@@ -3855,7 +3858,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B78" s="2">
         <v>46167.708333333336</v>
@@ -3882,7 +3885,7 @@
         <v>18</v>
       </c>
       <c r="J78" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K78" s="0" t="s">
         <v>20</v>
@@ -3890,7 +3893,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B79" s="2">
         <v>46167.708333333336</v>
@@ -3902,22 +3905,22 @@
         <v>34</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K79" s="0" t="s">
         <v>20</v>
@@ -3925,7 +3928,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B80" s="2">
         <v>46167.708333333336</v>
@@ -3937,22 +3940,22 @@
         <v>34</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I80" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J80" s="0" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K80" s="0" t="s">
         <v>20</v>
@@ -3960,7 +3963,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B81" s="2">
         <v>46167.802083333336</v>
@@ -3981,13 +3984,13 @@
         <v>52</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I81" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J81" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K81" s="0" t="s">
         <v>20</v>
@@ -3995,13 +3998,13 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B82" s="2">
         <v>46171.791666666664</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>56</v>
@@ -4010,19 +4013,19 @@
         <v>31</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>57</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I82" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J82" s="0" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K82" s="0" t="s">
         <v>20</v>
@@ -4030,13 +4033,13 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B83" s="2">
         <v>46171.791666666664</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>56</v>
@@ -4057,7 +4060,7 @@
         <v>18</v>
       </c>
       <c r="J83" s="0" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K83" s="0" t="s">
         <v>20</v>
@@ -4065,13 +4068,13 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B84" s="2">
         <v>46171.791666666664</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>56</v>
@@ -4092,7 +4095,7 @@
         <v>18</v>
       </c>
       <c r="J84" s="0" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K84" s="0" t="s">
         <v>20</v>
@@ -4100,13 +4103,13 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B85" s="2">
         <v>46171.791666666664</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>56</v>
@@ -4115,7 +4118,7 @@
         <v>35</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>50</v>
@@ -4127,7 +4130,7 @@
         <v>18</v>
       </c>
       <c r="J85" s="0" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K85" s="0" t="s">
         <v>20</v>
@@ -4135,13 +4138,13 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B86" s="2">
         <v>46171.791666666664</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>56</v>
@@ -4162,7 +4165,7 @@
         <v>18</v>
       </c>
       <c r="J86" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K86" s="0" t="s">
         <v>20</v>
@@ -4170,13 +4173,13 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B87" s="2">
         <v>46171.791666666664</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>56</v>
@@ -4197,7 +4200,7 @@
         <v>18</v>
       </c>
       <c r="J87" s="0" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K87" s="0" t="s">
         <v>20</v>
@@ -4205,7 +4208,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B88" s="2">
         <v>46172.666666666664</v>
@@ -4232,7 +4235,7 @@
         <v>18</v>
       </c>
       <c r="J88" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K88" s="0" t="s">
         <v>20</v>
@@ -4240,7 +4243,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B89" s="2">
         <v>46225.791666666664</v>
@@ -4255,7 +4258,7 @@
         <v>46</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>16</v>
@@ -4267,7 +4270,7 @@
         <v>18</v>
       </c>
       <c r="J89" s="0" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K89" s="0" t="s">
         <v>20</v>
@@ -4275,7 +4278,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B90" s="2">
         <v>46320.708333333336</v>
@@ -4290,7 +4293,7 @@
         <v>29</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>35</v>
@@ -4310,7 +4313,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B91" s="2">
         <v>46320.708333333336</v>
@@ -4325,7 +4328,7 @@
         <v>46</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>31</v>
@@ -4345,7 +4348,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B92" s="2">
         <v>46320.708333333336</v>
@@ -4357,16 +4360,16 @@
         <v>34</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I92" s="0" t="s">
         <v>18</v>
@@ -4380,7 +4383,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B93" s="2">
         <v>46320.708333333336</v>
@@ -4392,16 +4395,16 @@
         <v>34</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I93" s="0" t="s">
         <v>18</v>
@@ -4415,7 +4418,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B94" s="2">
         <v>46320.708333333336</v>
@@ -4430,7 +4433,7 @@
         <v>59</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>39</v>
@@ -4450,7 +4453,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B95" s="2">
         <v>46320.708333333336</v>
@@ -4462,16 +4465,16 @@
         <v>34</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I95" s="0" t="s">
         <v>18</v>
@@ -4485,7 +4488,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B96" s="2">
         <v>46320.708333333336</v>
@@ -4497,16 +4500,16 @@
         <v>34</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I96" s="0" t="s">
         <v>18</v>
@@ -4520,7 +4523,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B97" s="2">
         <v>46320.708333333336</v>
@@ -4535,7 +4538,7 @@
         <v>57</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>44</v>
@@ -4570,7 +4573,7 @@
         <v>52</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G98" s="0" t="s">
         <v>46</v>
@@ -4605,7 +4608,7 @@
         <v>44</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>22</v>
@@ -4640,7 +4643,7 @@
         <v>50</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>39</v>
@@ -4675,7 +4678,7 @@
         <v>35</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>59</v>
@@ -4710,13 +4713,13 @@
         <v>31</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>36</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I102" s="0" t="s">
         <v>18</v>
@@ -4745,13 +4748,13 @@
         <v>41</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>14</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>18</v>
@@ -4815,7 +4818,7 @@
         <v>57</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>16</v>
@@ -4850,7 +4853,7 @@
         <v>39</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>44</v>
@@ -4862,7 +4865,7 @@
         <v>18</v>
       </c>
       <c r="J106" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K106" s="0" t="s">
         <v>20</v>
@@ -4876,7 +4879,7 @@
         <v>46220.802083333336</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>49</v>
@@ -4885,7 +4888,7 @@
         <v>59</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>52</v>
@@ -4897,7 +4900,7 @@
         <v>18</v>
       </c>
       <c r="J107" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K107" s="0" t="s">
         <v>20</v>
@@ -4920,7 +4923,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>50</v>
@@ -4932,7 +4935,7 @@
         <v>18</v>
       </c>
       <c r="J108" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K108" s="0" t="s">
         <v>20</v>
@@ -4955,7 +4958,7 @@
         <v>46</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>35</v>
@@ -4967,7 +4970,7 @@
         <v>18</v>
       </c>
       <c r="J109" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K109" s="0" t="s">
         <v>20</v>
@@ -4990,7 +4993,7 @@
         <v>36</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>24</v>
@@ -5002,7 +5005,7 @@
         <v>18</v>
       </c>
       <c r="J110" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K110" s="0" t="s">
         <v>20</v>
@@ -5025,7 +5028,7 @@
         <v>29</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>57</v>
@@ -5037,7 +5040,7 @@
         <v>18</v>
       </c>
       <c r="J111" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K111" s="0" t="s">
         <v>20</v>
@@ -5060,7 +5063,7 @@
         <v>22</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>31</v>
@@ -5072,7 +5075,7 @@
         <v>18</v>
       </c>
       <c r="J112" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K112" s="0" t="s">
         <v>20</v>
@@ -5083,19 +5086,19 @@
         <v>199</v>
       </c>
       <c r="B113" s="2">
-        <v>46221.833333333336</v>
+        <v>46221.75</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>12</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E113" s="0" t="s">
         <v>16</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>41</v>
@@ -5107,7 +5110,7 @@
         <v>18</v>
       </c>
       <c r="J113" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K113" s="0" t="s">
         <v>20</v>
@@ -5115,7 +5118,7 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B114" s="2">
         <v>46127.791666666664</v>
@@ -5130,7 +5133,7 @@
         <v>50</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>46</v>
@@ -5142,7 +5145,7 @@
         <v>18</v>
       </c>
       <c r="J114" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K114" s="0" t="s">
         <v>20</v>
@@ -5150,7 +5153,7 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B115" s="2">
         <v>46228.666666666664</v>
@@ -5165,7 +5168,7 @@
         <v>29</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>36</v>
@@ -5177,7 +5180,7 @@
         <v>18</v>
       </c>
       <c r="J115" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K115" s="0" t="s">
         <v>20</v>
@@ -5185,7 +5188,7 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B116" s="2">
         <v>46229.604166666664</v>
@@ -5200,19 +5203,19 @@
         <v>31</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>39</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I116" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J116" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K116" s="0" t="s">
         <v>20</v>
@@ -5220,7 +5223,7 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B117" s="2">
         <v>46229.708333333336</v>
@@ -5232,22 +5235,22 @@
         <v>34</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="I117" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J117" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K117" s="0" t="s">
         <v>20</v>
@@ -5255,7 +5258,7 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B118" s="2">
         <v>46229.708333333336</v>
@@ -5267,22 +5270,22 @@
         <v>34</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I118" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J118" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K118" s="0" t="s">
         <v>20</v>
@@ -5290,7 +5293,7 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B119" s="2">
         <v>46229.708333333336</v>
@@ -5302,22 +5305,22 @@
         <v>34</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J119" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K119" s="0" t="s">
         <v>20</v>
@@ -5325,7 +5328,7 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B120" s="2">
         <v>46229.802083333336</v>
@@ -5340,7 +5343,7 @@
         <v>44</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>16</v>
@@ -5352,7 +5355,7 @@
         <v>18</v>
       </c>
       <c r="J120" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K120" s="0" t="s">
         <v>20</v>
@@ -5360,7 +5363,7 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B121" s="2">
         <v>46230.791666666664</v>
@@ -5375,7 +5378,7 @@
         <v>24</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>52</v>
@@ -5387,7 +5390,7 @@
         <v>18</v>
       </c>
       <c r="J121" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K121" s="0" t="s">
         <v>20</v>
@@ -5395,13 +5398,13 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B122" s="2">
         <v>46234.791666666664</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>56</v>
@@ -5410,7 +5413,7 @@
         <v>39</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>14</v>
@@ -5422,7 +5425,7 @@
         <v>18</v>
       </c>
       <c r="J122" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K122" s="0" t="s">
         <v>20</v>
@@ -5430,22 +5433,22 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B123" s="2">
         <v>46234.875</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E123" s="0" t="s">
         <v>59</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>46</v>
@@ -5457,7 +5460,7 @@
         <v>18</v>
       </c>
       <c r="J123" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K123" s="0" t="s">
         <v>20</v>
@@ -5465,7 +5468,7 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B124" s="2">
         <v>46235.666666666664</v>
@@ -5480,7 +5483,7 @@
         <v>52</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>41</v>
@@ -5492,7 +5495,7 @@
         <v>18</v>
       </c>
       <c r="J124" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K124" s="0" t="s">
         <v>20</v>
@@ -5500,7 +5503,7 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B125" s="2">
         <v>46235.75</v>
@@ -5515,7 +5518,7 @@
         <v>36</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>16</v>
@@ -5527,7 +5530,7 @@
         <v>18</v>
       </c>
       <c r="J125" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K125" s="0" t="s">
         <v>20</v>
@@ -5535,7 +5538,7 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B126" s="2">
         <v>46236.708333333336</v>
@@ -5550,7 +5553,7 @@
         <v>35</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>29</v>
@@ -5562,7 +5565,7 @@
         <v>18</v>
       </c>
       <c r="J126" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K126" s="0" t="s">
         <v>20</v>
@@ -5570,7 +5573,7 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B127" s="2">
         <v>46236.708333333336</v>
@@ -5585,7 +5588,7 @@
         <v>22</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>57</v>
@@ -5597,7 +5600,7 @@
         <v>18</v>
       </c>
       <c r="J127" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K127" s="0" t="s">
         <v>20</v>
@@ -5605,7 +5608,7 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B128" s="2">
         <v>46236.708333333336</v>
@@ -5620,7 +5623,7 @@
         <v>44</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>50</v>
@@ -5632,7 +5635,7 @@
         <v>18</v>
       </c>
       <c r="J128" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K128" s="0" t="s">
         <v>20</v>
@@ -5640,7 +5643,7 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B129" s="2">
         <v>46236.802083333336</v>
@@ -5655,19 +5658,19 @@
         <v>31</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>24</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I129" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J129" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K129" s="0" t="s">
         <v>20</v>
@@ -5675,7 +5678,7 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B130" s="2">
         <v>46141.791666666664</v>
@@ -5690,7 +5693,7 @@
         <v>50</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>31</v>
@@ -5702,7 +5705,7 @@
         <v>18</v>
       </c>
       <c r="J130" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K130" s="0" t="s">
         <v>20</v>
@@ -5710,13 +5713,13 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B131" s="2">
         <v>46241.791666666664</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>56</v>
@@ -5725,19 +5728,19 @@
         <v>41</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>35</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I131" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J131" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K131" s="0" t="s">
         <v>20</v>
@@ -5745,7 +5748,7 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B132" s="2">
         <v>46242.583333333336</v>
@@ -5760,7 +5763,7 @@
         <v>39</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>59</v>
@@ -5772,7 +5775,7 @@
         <v>18</v>
       </c>
       <c r="J132" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K132" s="0" t="s">
         <v>20</v>
@@ -5780,7 +5783,7 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B133" s="2">
         <v>46242.666666666664</v>
@@ -5795,7 +5798,7 @@
         <v>16</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>57</v>
@@ -5807,7 +5810,7 @@
         <v>18</v>
       </c>
       <c r="J133" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K133" s="0" t="s">
         <v>20</v>
@@ -5815,7 +5818,7 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B134" s="2">
         <v>46242.75</v>
@@ -5830,7 +5833,7 @@
         <v>36</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>52</v>
@@ -5842,7 +5845,7 @@
         <v>18</v>
       </c>
       <c r="J134" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K134" s="0" t="s">
         <v>20</v>
@@ -5850,7 +5853,7 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B135" s="2">
         <v>46243.604166666664</v>
@@ -5865,7 +5868,7 @@
         <v>46</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>24</v>
@@ -5877,7 +5880,7 @@
         <v>18</v>
       </c>
       <c r="J135" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K135" s="0" t="s">
         <v>20</v>
@@ -5885,7 +5888,7 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B136" s="2">
         <v>46243.708333333336</v>
@@ -5900,7 +5903,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>44</v>
@@ -5912,7 +5915,7 @@
         <v>18</v>
       </c>
       <c r="J136" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K136" s="0" t="s">
         <v>20</v>
@@ -5920,7 +5923,7 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B137" s="2">
         <v>46243.802083333336</v>
@@ -5935,7 +5938,7 @@
         <v>29</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>22</v>
@@ -5947,7 +5950,7 @@
         <v>18</v>
       </c>
       <c r="J137" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K137" s="0" t="s">
         <v>20</v>
@@ -5955,7 +5958,7 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B138" s="2">
         <v>46142.791666666664</v>
@@ -5982,7 +5985,7 @@
         <v>18</v>
       </c>
       <c r="J138" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K138" s="0" t="s">
         <v>20</v>
@@ -5990,13 +5993,13 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B139" s="2">
         <v>46248.791666666664</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>56</v>
@@ -6005,7 +6008,7 @@
         <v>24</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>16</v>
@@ -6017,7 +6020,7 @@
         <v>18</v>
       </c>
       <c r="J139" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K139" s="0" t="s">
         <v>20</v>
@@ -6025,7 +6028,7 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B140" s="2">
         <v>46249.666666666664</v>
@@ -6040,7 +6043,7 @@
         <v>35</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>46</v>
@@ -6052,7 +6055,7 @@
         <v>18</v>
       </c>
       <c r="J140" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K140" s="0" t="s">
         <v>20</v>
@@ -6060,7 +6063,7 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B141" s="2">
         <v>46250.604166666664</v>
@@ -6075,7 +6078,7 @@
         <v>44</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G141" s="0" t="s">
         <v>39</v>
@@ -6087,7 +6090,7 @@
         <v>18</v>
       </c>
       <c r="J141" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K141" s="0" t="s">
         <v>20</v>
@@ -6095,7 +6098,7 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B142" s="2">
         <v>46250.708333333336</v>
@@ -6110,7 +6113,7 @@
         <v>22</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>50</v>
@@ -6122,7 +6125,7 @@
         <v>18</v>
       </c>
       <c r="J142" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K142" s="0" t="s">
         <v>20</v>
@@ -6130,7 +6133,7 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B143" s="2">
         <v>46250.708333333336</v>
@@ -6145,7 +6148,7 @@
         <v>57</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>41</v>
@@ -6157,7 +6160,7 @@
         <v>18</v>
       </c>
       <c r="J143" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K143" s="0" t="s">
         <v>20</v>
@@ -6165,7 +6168,7 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B144" s="2">
         <v>46250.708333333336</v>
@@ -6180,19 +6183,19 @@
         <v>31</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>14</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I144" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J144" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K144" s="0" t="s">
         <v>20</v>
@@ -6200,7 +6203,7 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B145" s="2">
         <v>46250.802083333336</v>
@@ -6215,7 +6218,7 @@
         <v>52</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>29</v>
@@ -6227,7 +6230,7 @@
         <v>18</v>
       </c>
       <c r="J145" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K145" s="0" t="s">
         <v>20</v>
@@ -6235,7 +6238,7 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B146" s="2">
         <v>46263.666666666664</v>
@@ -6250,7 +6253,7 @@
         <v>39</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>22</v>
@@ -6262,7 +6265,7 @@
         <v>18</v>
       </c>
       <c r="J146" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K146" s="0" t="s">
         <v>20</v>
@@ -6270,7 +6273,7 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B147" s="2">
         <v>46263.75</v>
@@ -6285,7 +6288,7 @@
         <v>16</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>44</v>
@@ -6297,7 +6300,7 @@
         <v>18</v>
       </c>
       <c r="J147" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K147" s="0" t="s">
         <v>20</v>
@@ -6305,7 +6308,7 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B148" s="2">
         <v>46264.604166666664</v>
@@ -6320,7 +6323,7 @@
         <v>59</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>24</v>
@@ -6332,7 +6335,7 @@
         <v>18</v>
       </c>
       <c r="J148" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K148" s="0" t="s">
         <v>20</v>
@@ -6340,7 +6343,7 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B149" s="2">
         <v>46264.708333333336</v>
@@ -6355,7 +6358,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>29</v>
@@ -6367,7 +6370,7 @@
         <v>18</v>
       </c>
       <c r="J149" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K149" s="0" t="s">
         <v>20</v>
@@ -6375,7 +6378,7 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B150" s="2">
         <v>46264.708333333336</v>
@@ -6390,19 +6393,19 @@
         <v>41</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>31</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I150" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J150" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K150" s="0" t="s">
         <v>20</v>
@@ -6410,7 +6413,7 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B151" s="2">
         <v>46264.708333333336</v>
@@ -6425,7 +6428,7 @@
         <v>36</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>35</v>
@@ -6437,7 +6440,7 @@
         <v>18</v>
       </c>
       <c r="J151" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K151" s="0" t="s">
         <v>20</v>
@@ -6445,7 +6448,7 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B152" s="2">
         <v>46264.708333333336</v>
@@ -6460,7 +6463,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>57</v>
@@ -6472,7 +6475,7 @@
         <v>18</v>
       </c>
       <c r="J152" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K152" s="0" t="s">
         <v>20</v>
@@ -6480,7 +6483,7 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B153" s="2">
         <v>46264.802083333336</v>
@@ -6495,7 +6498,7 @@
         <v>46</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>52</v>
@@ -6507,7 +6510,7 @@
         <v>18</v>
       </c>
       <c r="J153" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K153" s="0" t="s">
         <v>20</v>
@@ -6515,13 +6518,13 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B154" s="2">
         <v>46269.791666666664</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>56</v>
@@ -6530,7 +6533,7 @@
         <v>52</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>59</v>
@@ -6542,7 +6545,7 @@
         <v>18</v>
       </c>
       <c r="J154" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K154" s="0" t="s">
         <v>20</v>
@@ -6550,34 +6553,34 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B155" s="2">
-        <v>46269.875</v>
+        <v>46269.791666666664</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="I155" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J155" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K155" s="0" t="s">
         <v>20</v>
@@ -6585,34 +6588,34 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B156" s="2">
-        <v>46270.666666666664</v>
+        <v>46269.875</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>13</v>
+        <v>221</v>
       </c>
       <c r="E156" s="0" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G156" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J156" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K156" s="0" t="s">
         <v>20</v>
@@ -6620,34 +6623,34 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B157" s="2">
-        <v>46270.75</v>
+        <v>46270.666666666664</v>
       </c>
       <c r="C157" s="0" t="s">
         <v>12</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I157" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J157" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K157" s="0" t="s">
         <v>20</v>
@@ -6655,34 +6658,34 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B158" s="2">
-        <v>46271.708333333336</v>
+        <v>46270.75</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E158" s="0" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="I158" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J158" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K158" s="0" t="s">
         <v>20</v>
@@ -6690,7 +6693,7 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B159" s="2">
         <v>46271.708333333336</v>
@@ -6705,7 +6708,7 @@
         <v>22</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>35</v>
@@ -6717,7 +6720,7 @@
         <v>18</v>
       </c>
       <c r="J159" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K159" s="0" t="s">
         <v>20</v>
@@ -6725,7 +6728,7 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B160" s="2">
         <v>46271.802083333336</v>
@@ -6740,7 +6743,7 @@
         <v>29</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>50</v>
@@ -6752,7 +6755,7 @@
         <v>18</v>
       </c>
       <c r="J160" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K160" s="0" t="s">
         <v>20</v>
@@ -6760,7 +6763,7 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B161" s="2">
         <v>46272.791666666664</v>
@@ -6775,7 +6778,7 @@
         <v>57</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>39</v>
@@ -6787,7 +6790,7 @@
         <v>18</v>
       </c>
       <c r="J161" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K161" s="0" t="s">
         <v>20</v>
@@ -6795,7 +6798,7 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B162" s="2">
         <v>46277.666666666664</v>
@@ -6810,7 +6813,7 @@
         <v>46</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>39</v>
@@ -6822,7 +6825,7 @@
         <v>18</v>
       </c>
       <c r="J162" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K162" s="0" t="s">
         <v>20</v>
@@ -6830,7 +6833,7 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B163" s="2">
         <v>46277.75</v>
@@ -6845,7 +6848,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>50</v>
@@ -6857,7 +6860,7 @@
         <v>18</v>
       </c>
       <c r="J163" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K163" s="0" t="s">
         <v>20</v>
@@ -6865,7 +6868,7 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B164" s="2">
         <v>46278.604166666664</v>
@@ -6880,7 +6883,7 @@
         <v>16</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>29</v>
@@ -6892,7 +6895,7 @@
         <v>18</v>
       </c>
       <c r="J164" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K164" s="0" t="s">
         <v>20</v>
@@ -6900,7 +6903,7 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B165" s="2">
         <v>46278.708333333336</v>
@@ -6915,7 +6918,7 @@
         <v>35</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>44</v>
@@ -6927,7 +6930,7 @@
         <v>18</v>
       </c>
       <c r="J165" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K165" s="0" t="s">
         <v>20</v>
@@ -6935,7 +6938,7 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B166" s="2">
         <v>46278.708333333336</v>
@@ -6950,7 +6953,7 @@
         <v>36</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>31</v>
@@ -6962,7 +6965,7 @@
         <v>18</v>
       </c>
       <c r="J166" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K166" s="0" t="s">
         <v>20</v>
@@ -6970,7 +6973,7 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B167" s="2">
         <v>46278.708333333336</v>
@@ -6985,7 +6988,7 @@
         <v>59</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>41</v>
@@ -6997,7 +7000,7 @@
         <v>18</v>
       </c>
       <c r="J167" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K167" s="0" t="s">
         <v>20</v>
@@ -7005,7 +7008,7 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B168" s="2">
         <v>46278.708333333336</v>
@@ -7020,7 +7023,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>22</v>
@@ -7032,7 +7035,7 @@
         <v>18</v>
       </c>
       <c r="J168" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K168" s="0" t="s">
         <v>20</v>
@@ -7040,7 +7043,7 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B169" s="2">
         <v>46278.802083333336</v>
@@ -7055,7 +7058,7 @@
         <v>52</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>57</v>
@@ -7067,7 +7070,7 @@
         <v>18</v>
       </c>
       <c r="J169" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K169" s="0" t="s">
         <v>20</v>
@@ -7075,13 +7078,13 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B170" s="2">
         <v>46283.791666666664</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>56</v>
@@ -7090,7 +7093,7 @@
         <v>57</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>35</v>
@@ -7102,7 +7105,7 @@
         <v>18</v>
       </c>
       <c r="J170" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K170" s="0" t="s">
         <v>20</v>
@@ -7110,7 +7113,7 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B171" s="2">
         <v>46284.666666666664</v>
@@ -7125,7 +7128,7 @@
         <v>29</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>24</v>
@@ -7137,7 +7140,7 @@
         <v>18</v>
       </c>
       <c r="J171" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K171" s="0" t="s">
         <v>20</v>
@@ -7145,7 +7148,7 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B172" s="2">
         <v>46284.75</v>
@@ -7160,7 +7163,7 @@
         <v>22</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>44</v>
@@ -7172,7 +7175,7 @@
         <v>18</v>
       </c>
       <c r="J172" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K172" s="0" t="s">
         <v>20</v>
@@ -7180,7 +7183,7 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B173" s="2">
         <v>46285.604166666664</v>
@@ -7195,7 +7198,7 @@
         <v>39</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>52</v>
@@ -7207,7 +7210,7 @@
         <v>18</v>
       </c>
       <c r="J173" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K173" s="0" t="s">
         <v>20</v>
@@ -7215,7 +7218,7 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B174" s="2">
         <v>46285.708333333336</v>
@@ -7230,19 +7233,19 @@
         <v>41</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>36</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I174" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J174" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K174" s="0" t="s">
         <v>20</v>
@@ -7250,7 +7253,7 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B175" s="2">
         <v>46285.708333333336</v>
@@ -7265,7 +7268,7 @@
         <v>50</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>14</v>
@@ -7277,7 +7280,7 @@
         <v>18</v>
       </c>
       <c r="J175" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K175" s="0" t="s">
         <v>20</v>
@@ -7285,7 +7288,7 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B176" s="2">
         <v>46285.708333333336</v>
@@ -7300,7 +7303,7 @@
         <v>16</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>46</v>
@@ -7312,7 +7315,7 @@
         <v>18</v>
       </c>
       <c r="J176" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K176" s="0" t="s">
         <v>20</v>
@@ -7320,7 +7323,7 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B177" s="2">
         <v>46285.802083333336</v>
@@ -7335,19 +7338,19 @@
         <v>31</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>59</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I177" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J177" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K177" s="0" t="s">
         <v>20</v>
@@ -7355,7 +7358,7 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B178" s="2">
         <v>46306.708333333336</v>
@@ -7367,22 +7370,22 @@
         <v>34</v>
       </c>
       <c r="E178" s="0" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J178" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K178" s="0" t="s">
         <v>20</v>
@@ -7390,7 +7393,7 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B179" s="2">
         <v>46306.708333333336</v>
@@ -7402,22 +7405,22 @@
         <v>34</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="I179" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J179" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K179" s="0" t="s">
         <v>20</v>
@@ -7425,7 +7428,7 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B180" s="2">
         <v>46306.708333333336</v>
@@ -7437,22 +7440,22 @@
         <v>34</v>
       </c>
       <c r="E180" s="0" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I180" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J180" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K180" s="0" t="s">
         <v>20</v>
@@ -7460,7 +7463,7 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B181" s="2">
         <v>46306.708333333336</v>
@@ -7472,22 +7475,22 @@
         <v>34</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G181" s="0" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J181" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K181" s="0" t="s">
         <v>20</v>
@@ -7495,7 +7498,7 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B182" s="2">
         <v>46306.708333333336</v>
@@ -7507,22 +7510,22 @@
         <v>34</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="I182" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J182" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K182" s="0" t="s">
         <v>20</v>
@@ -7530,7 +7533,7 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B183" s="2">
         <v>46306.708333333336</v>
@@ -7542,22 +7545,22 @@
         <v>34</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G183" s="0" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I183" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J183" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K183" s="0" t="s">
         <v>20</v>
@@ -7565,7 +7568,7 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B184" s="2">
         <v>46306.708333333336</v>
@@ -7580,7 +7583,7 @@
         <v>36</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>14</v>
@@ -7592,7 +7595,7 @@
         <v>18</v>
       </c>
       <c r="J184" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K184" s="0" t="s">
         <v>20</v>
@@ -7600,7 +7603,7 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B185" s="2">
         <v>46306.708333333336</v>
@@ -7615,7 +7618,7 @@
         <v>44</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>57</v>
@@ -7627,7 +7630,7 @@
         <v>18</v>
       </c>
       <c r="J185" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K185" s="0" t="s">
         <v>20</v>
@@ -7635,7 +7638,7 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B186" s="2">
         <v>46313.708333333336</v>
@@ -7650,7 +7653,7 @@
         <v>29</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G186" s="0" t="s">
         <v>44</v>
@@ -7662,7 +7665,7 @@
         <v>18</v>
       </c>
       <c r="J186" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K186" s="0" t="s">
         <v>20</v>
@@ -7670,7 +7673,7 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B187" s="2">
         <v>46313.708333333336</v>
@@ -7685,7 +7688,7 @@
         <v>57</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>24</v>
@@ -7697,7 +7700,7 @@
         <v>18</v>
       </c>
       <c r="J187" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K187" s="0" t="s">
         <v>20</v>
@@ -7705,7 +7708,7 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B188" s="2">
         <v>46313.708333333336</v>
@@ -7720,7 +7723,7 @@
         <v>39</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>31</v>
@@ -7732,7 +7735,7 @@
         <v>18</v>
       </c>
       <c r="J188" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K188" s="0" t="s">
         <v>20</v>
@@ -7740,7 +7743,7 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B189" s="2">
         <v>46313.708333333336</v>
@@ -7755,7 +7758,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>59</v>
@@ -7767,7 +7770,7 @@
         <v>18</v>
       </c>
       <c r="J189" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K189" s="0" t="s">
         <v>20</v>
@@ -7775,7 +7778,7 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B190" s="2">
         <v>46313.708333333336</v>
@@ -7787,22 +7790,22 @@
         <v>34</v>
       </c>
       <c r="E190" s="0" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="I190" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J190" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K190" s="0" t="s">
         <v>20</v>
@@ -7810,7 +7813,7 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B191" s="2">
         <v>46313.708333333336</v>
@@ -7822,22 +7825,22 @@
         <v>34</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G191" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="I191" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J191" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K191" s="0" t="s">
         <v>20</v>
@@ -7845,7 +7848,7 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B192" s="2">
         <v>46313.708333333336</v>
@@ -7857,22 +7860,22 @@
         <v>34</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J192" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K192" s="0" t="s">
         <v>20</v>
@@ -7880,7 +7883,7 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B193" s="2">
         <v>46313.708333333336</v>
@@ -7895,7 +7898,7 @@
         <v>16</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>52</v>
@@ -7907,7 +7910,7 @@
         <v>18</v>
       </c>
       <c r="J193" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K193" s="0" t="s">
         <v>20</v>
@@ -7915,7 +7918,7 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B194" s="2">
         <v>46327.708333333336</v>
@@ -7927,22 +7930,22 @@
         <v>34</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="I194" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J194" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K194" s="0" t="s">
         <v>20</v>
@@ -7950,7 +7953,7 @@
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B195" s="2">
         <v>46327.708333333336</v>
@@ -7962,22 +7965,22 @@
         <v>34</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J195" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K195" s="0" t="s">
         <v>20</v>
@@ -7985,7 +7988,7 @@
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B196" s="2">
         <v>46327.708333333336</v>
@@ -7997,22 +8000,22 @@
         <v>34</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J196" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K196" s="0" t="s">
         <v>20</v>
@@ -8020,7 +8023,7 @@
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B197" s="2">
         <v>46327.708333333336</v>
@@ -8032,22 +8035,22 @@
         <v>34</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J197" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K197" s="0" t="s">
         <v>20</v>
@@ -8055,7 +8058,7 @@
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B198" s="2">
         <v>46327.708333333336</v>
@@ -8067,22 +8070,22 @@
         <v>34</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J198" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K198" s="0" t="s">
         <v>20</v>
@@ -8090,7 +8093,7 @@
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B199" s="2">
         <v>46327.708333333336</v>
@@ -8102,22 +8105,22 @@
         <v>34</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G199" s="0" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="I199" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J199" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K199" s="0" t="s">
         <v>20</v>
@@ -8125,7 +8128,7 @@
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B200" s="2">
         <v>46327.708333333336</v>
@@ -8137,22 +8140,22 @@
         <v>34</v>
       </c>
       <c r="E200" s="0" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I200" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J200" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K200" s="0" t="s">
         <v>20</v>
@@ -8160,7 +8163,7 @@
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B201" s="2">
         <v>46327.708333333336</v>
@@ -8175,7 +8178,7 @@
         <v>44</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>41</v>
@@ -8187,7 +8190,7 @@
         <v>18</v>
       </c>
       <c r="J201" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K201" s="0" t="s">
         <v>20</v>
@@ -8195,7 +8198,7 @@
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B202" s="2">
         <v>46334.708333333336</v>
@@ -8210,7 +8213,7 @@
         <v>24</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>36</v>
@@ -8222,7 +8225,7 @@
         <v>18</v>
       </c>
       <c r="J202" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K202" s="0" t="s">
         <v>20</v>
@@ -8230,7 +8233,7 @@
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B203" s="2">
         <v>46334.708333333336</v>
@@ -8245,19 +8248,19 @@
         <v>41</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>22</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I203" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J203" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K203" s="0" t="s">
         <v>20</v>
@@ -8265,7 +8268,7 @@
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B204" s="2">
         <v>46334.708333333336</v>
@@ -8280,7 +8283,7 @@
         <v>16</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>35</v>
@@ -8292,7 +8295,7 @@
         <v>18</v>
       </c>
       <c r="J204" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K204" s="0" t="s">
         <v>20</v>
@@ -8300,7 +8303,7 @@
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B205" s="2">
         <v>46334.708333333336</v>
@@ -8315,7 +8318,7 @@
         <v>52</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>31</v>
@@ -8327,7 +8330,7 @@
         <v>18</v>
       </c>
       <c r="J205" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K205" s="0" t="s">
         <v>20</v>
@@ -8335,7 +8338,7 @@
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B206" s="2">
         <v>46334.708333333336</v>
@@ -8350,7 +8353,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>57</v>
@@ -8362,7 +8365,7 @@
         <v>18</v>
       </c>
       <c r="J206" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K206" s="0" t="s">
         <v>20</v>
@@ -8370,7 +8373,7 @@
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B207" s="2">
         <v>46334.708333333336</v>
@@ -8385,7 +8388,7 @@
         <v>29</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G207" s="0" t="s">
         <v>39</v>
@@ -8397,7 +8400,7 @@
         <v>18</v>
       </c>
       <c r="J207" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K207" s="0" t="s">
         <v>20</v>
@@ -8405,7 +8408,7 @@
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B208" s="2">
         <v>46334.708333333336</v>
@@ -8420,7 +8423,7 @@
         <v>46</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G208" s="0" t="s">
         <v>44</v>
@@ -8432,7 +8435,7 @@
         <v>18</v>
       </c>
       <c r="J208" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K208" s="0" t="s">
         <v>20</v>
@@ -8440,7 +8443,7 @@
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B209" s="2">
         <v>46334.708333333336</v>
@@ -8455,7 +8458,7 @@
         <v>50</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G209" s="0" t="s">
         <v>59</v>
@@ -8467,7 +8470,7 @@
         <v>18</v>
       </c>
       <c r="J209" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K209" s="0" t="s">
         <v>20</v>
@@ -8475,7 +8478,7 @@
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B210" s="2">
         <v>46348.708333333336</v>
@@ -8490,7 +8493,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>52</v>
@@ -8502,7 +8505,7 @@
         <v>18</v>
       </c>
       <c r="J210" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K210" s="0" t="s">
         <v>20</v>
@@ -8510,7 +8513,7 @@
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B211" s="2">
         <v>46348.708333333336</v>
@@ -8525,7 +8528,7 @@
         <v>29</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>41</v>
@@ -8537,7 +8540,7 @@
         <v>18</v>
       </c>
       <c r="J211" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K211" s="0" t="s">
         <v>20</v>
@@ -8545,7 +8548,7 @@
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B212" s="2">
         <v>46348.708333333336</v>
@@ -8560,7 +8563,7 @@
         <v>57</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>46</v>
@@ -8572,7 +8575,7 @@
         <v>18</v>
       </c>
       <c r="J212" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K212" s="0" t="s">
         <v>20</v>
@@ -8580,7 +8583,7 @@
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B213" s="2">
         <v>46348.708333333336</v>
@@ -8595,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>16</v>
@@ -8607,7 +8610,7 @@
         <v>18</v>
       </c>
       <c r="J213" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K213" s="0" t="s">
         <v>20</v>
@@ -8615,7 +8618,7 @@
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B214" s="2">
         <v>46348.708333333336</v>
@@ -8627,22 +8630,22 @@
         <v>34</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G214" s="0" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I214" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J214" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K214" s="0" t="s">
         <v>20</v>
@@ -8650,7 +8653,7 @@
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B215" s="2">
         <v>46348.708333333336</v>
@@ -8662,22 +8665,22 @@
         <v>34</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G215" s="0" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I215" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J215" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K215" s="0" t="s">
         <v>20</v>
@@ -8685,7 +8688,7 @@
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B216" s="2">
         <v>46348.708333333336</v>
@@ -8697,22 +8700,22 @@
         <v>34</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="I216" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J216" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K216" s="0" t="s">
         <v>20</v>
@@ -8720,7 +8723,7 @@
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B217" s="2">
         <v>46348.708333333336</v>
@@ -8732,22 +8735,22 @@
         <v>34</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I217" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J217" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K217" s="0" t="s">
         <v>20</v>
@@ -8755,7 +8758,7 @@
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B218" s="2">
         <v>46355.708333333336</v>
@@ -8770,19 +8773,19 @@
         <v>31</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>29</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I218" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J218" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K218" s="0" t="s">
         <v>20</v>
@@ -8790,7 +8793,7 @@
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B219" s="2">
         <v>46355.708333333336</v>
@@ -8805,7 +8808,7 @@
         <v>24</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>22</v>
@@ -8817,7 +8820,7 @@
         <v>18</v>
       </c>
       <c r="J219" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K219" s="0" t="s">
         <v>20</v>
@@ -8825,7 +8828,7 @@
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B220" s="2">
         <v>46355.708333333336</v>
@@ -8840,19 +8843,19 @@
         <v>41</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G220" s="0" t="s">
         <v>50</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I220" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J220" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K220" s="0" t="s">
         <v>20</v>
@@ -8860,7 +8863,7 @@
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B221" s="2">
         <v>46355.708333333336</v>
@@ -8875,7 +8878,7 @@
         <v>36</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>57</v>
@@ -8887,7 +8890,7 @@
         <v>18</v>
       </c>
       <c r="J221" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K221" s="0" t="s">
         <v>20</v>
@@ -8895,7 +8898,7 @@
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B222" s="2">
         <v>46355.708333333336</v>
@@ -8910,7 +8913,7 @@
         <v>59</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>35</v>
@@ -8922,7 +8925,7 @@
         <v>18</v>
       </c>
       <c r="J222" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K222" s="0" t="s">
         <v>20</v>
@@ -8930,7 +8933,7 @@
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B223" s="2">
         <v>46355.708333333336</v>
@@ -8945,7 +8948,7 @@
         <v>52</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>44</v>
@@ -8957,7 +8960,7 @@
         <v>18</v>
       </c>
       <c r="J223" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K223" s="0" t="s">
         <v>20</v>
@@ -8965,7 +8968,7 @@
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B224" s="2">
         <v>46355.708333333336</v>
@@ -8980,7 +8983,7 @@
         <v>46</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>14</v>
@@ -8992,7 +8995,7 @@
         <v>18</v>
       </c>
       <c r="J224" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K224" s="0" t="s">
         <v>20</v>
@@ -9000,7 +9003,7 @@
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B225" s="2">
         <v>46355.708333333336</v>
@@ -9015,7 +9018,7 @@
         <v>16</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>39</v>
@@ -9027,7 +9030,7 @@
         <v>18</v>
       </c>
       <c r="J225" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K225" s="0" t="s">
         <v>20</v>
@@ -9035,7 +9038,7 @@
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B226" s="2">
         <v>46362.708333333336</v>
@@ -9050,7 +9053,7 @@
         <v>44</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>59</v>
@@ -9062,7 +9065,7 @@
         <v>18</v>
       </c>
       <c r="J226" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K226" s="0" t="s">
         <v>20</v>
@@ -9070,7 +9073,7 @@
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B227" s="2">
         <v>46362.708333333336</v>
@@ -9085,7 +9088,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>41</v>
@@ -9097,7 +9100,7 @@
         <v>18</v>
       </c>
       <c r="J227" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K227" s="0" t="s">
         <v>20</v>
@@ -9105,7 +9108,7 @@
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B228" s="2">
         <v>46362.708333333336</v>
@@ -9117,22 +9120,22 @@
         <v>34</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I228" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J228" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K228" s="0" t="s">
         <v>20</v>
@@ -9140,7 +9143,7 @@
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B229" s="2">
         <v>46362.708333333336</v>
@@ -9152,22 +9155,22 @@
         <v>34</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="I229" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J229" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K229" s="0" t="s">
         <v>20</v>
@@ -9175,7 +9178,7 @@
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B230" s="2">
         <v>46362.708333333336</v>
@@ -9187,22 +9190,22 @@
         <v>34</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="I230" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J230" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K230" s="0" t="s">
         <v>20</v>
@@ -9210,7 +9213,7 @@
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B231" s="2">
         <v>46362.708333333336</v>
@@ -9222,22 +9225,22 @@
         <v>34</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="I231" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J231" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K231" s="0" t="s">
         <v>20</v>
@@ -9245,7 +9248,7 @@
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B232" s="2">
         <v>46362.708333333336</v>
@@ -9257,22 +9260,22 @@
         <v>34</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I232" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J232" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K232" s="0" t="s">
         <v>20</v>
@@ -9280,7 +9283,7 @@
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B233" s="2">
         <v>46362.708333333336</v>
@@ -9292,22 +9295,22 @@
         <v>34</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I233" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J233" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K233" s="0" t="s">
         <v>20</v>
@@ -9315,7 +9318,7 @@
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B234" s="2">
         <v>46369.708333333336</v>
@@ -9327,22 +9330,22 @@
         <v>34</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="I234" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J234" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K234" s="0" t="s">
         <v>20</v>
@@ -9350,7 +9353,7 @@
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B235" s="2">
         <v>46369.708333333336</v>
@@ -9362,22 +9365,22 @@
         <v>34</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="I235" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J235" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K235" s="0" t="s">
         <v>20</v>
@@ -9385,7 +9388,7 @@
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B236" s="2">
         <v>46369.708333333336</v>
@@ -9397,22 +9400,22 @@
         <v>34</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I236" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J236" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K236" s="0" t="s">
         <v>20</v>
@@ -9420,7 +9423,7 @@
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B237" s="2">
         <v>46369.708333333336</v>
@@ -9432,22 +9435,22 @@
         <v>34</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G237" s="0" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="I237" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J237" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K237" s="0" t="s">
         <v>20</v>
@@ -9455,7 +9458,7 @@
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B238" s="2">
         <v>46369.708333333336</v>
@@ -9467,22 +9470,22 @@
         <v>34</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F238" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G238" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I238" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J238" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K238" s="0" t="s">
         <v>20</v>
@@ -9490,7 +9493,7 @@
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B239" s="2">
         <v>46369.708333333336</v>
@@ -9505,19 +9508,19 @@
         <v>31</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G239" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I239" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J239" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K239" s="0" t="s">
         <v>20</v>
@@ -9525,7 +9528,7 @@
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B240" s="2">
         <v>46369.708333333336</v>
@@ -9540,7 +9543,7 @@
         <v>46</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>50</v>
@@ -9552,7 +9555,7 @@
         <v>18</v>
       </c>
       <c r="J240" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K240" s="0" t="s">
         <v>20</v>
@@ -9560,7 +9563,7 @@
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B241" s="2">
         <v>46369.708333333336</v>
@@ -9575,19 +9578,19 @@
         <v>41</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="G241" s="0" t="s">
         <v>39</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I241" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J241" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K241" s="0" t="s">
         <v>20</v>

--- a/data/kamper_2026.xlsx
+++ b/data/kamper_2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
   <si>
     <t>Runde</t>
   </si>
@@ -131,6 +131,21 @@
     <t>99120001002</t>
   </si>
   <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>1 - 3</t>
+  </si>
+  <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Color Line Stadion</t>
+  </si>
+  <si>
+    <t>99120001008</t>
+  </si>
+  <si>
     <t>Vålerenga</t>
   </si>
   <si>
@@ -146,21 +161,6 @@
     <t>99120001007</t>
   </si>
   <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>1 - 3</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Color Line Stadion</t>
-  </si>
-  <si>
-    <t>99120001008</t>
-  </si>
-  <si>
     <t>19:15</t>
   </si>
   <si>
@@ -236,21 +236,21 @@
     <t>99120001011</t>
   </si>
   <si>
+    <t>1 - 2</t>
+  </si>
+  <si>
+    <t>Brann stadion</t>
+  </si>
+  <si>
+    <t>99120001010</t>
+  </si>
+  <si>
     <t>Jotun Arena</t>
   </si>
   <si>
     <t>99120001014</t>
   </si>
   <si>
-    <t>1 - 2</t>
-  </si>
-  <si>
-    <t>Brann stadion</t>
-  </si>
-  <si>
-    <t>99120001010</t>
-  </si>
-  <si>
     <t>Åråsen stadion</t>
   </si>
   <si>
@@ -392,12 +392,12 @@
     <t>99120001045</t>
   </si>
   <si>
+    <t>99120001048</t>
+  </si>
+  <si>
     <t>99120001047</t>
   </si>
   <si>
-    <t>99120001048</t>
-  </si>
-  <si>
     <t>99120001042</t>
   </si>
   <si>
@@ -425,12 +425,12 @@
     <t>99120001051</t>
   </si>
   <si>
+    <t>99120001054</t>
+  </si>
+  <si>
     <t>99120001053</t>
   </si>
   <si>
-    <t>99120001054</t>
-  </si>
-  <si>
     <t>99120001056</t>
   </si>
   <si>
@@ -449,12 +449,12 @@
     <t>99120001059</t>
   </si>
   <si>
+    <t>99120001063</t>
+  </si>
+  <si>
     <t>99120001060</t>
   </si>
   <si>
-    <t>99120001063</t>
-  </si>
-  <si>
     <t>99120001058</t>
   </si>
   <si>
@@ -476,24 +476,24 @@
     <t>99120001066</t>
   </si>
   <si>
+    <t>99120001070</t>
+  </si>
+  <si>
     <t>99120001068</t>
   </si>
   <si>
-    <t>99120001070</t>
-  </si>
-  <si>
     <t>99120001067</t>
   </si>
   <si>
+    <t>99120001069</t>
+  </si>
+  <si>
     <t>6 - 3</t>
   </si>
   <si>
     <t>99120001071</t>
   </si>
   <si>
-    <t>99120001069</t>
-  </si>
-  <si>
     <t>99120001065</t>
   </si>
   <si>
@@ -518,12 +518,12 @@
     <t>99120001075</t>
   </si>
   <si>
+    <t>99120001078</t>
+  </si>
+  <si>
     <t>99120001080</t>
   </si>
   <si>
-    <t>99120001078</t>
-  </si>
-  <si>
     <t>99120001077</t>
   </si>
   <si>
@@ -566,12 +566,12 @@
     <t>99120001092</t>
   </si>
   <si>
+    <t>99120001096</t>
+  </si>
+  <si>
     <t>99120001095</t>
   </si>
   <si>
-    <t>99120001096</t>
-  </si>
-  <si>
     <t>99120001089</t>
   </si>
   <si>
@@ -656,15 +656,18 @@
     <t>99120001113</t>
   </si>
   <si>
+    <t>99120001118</t>
+  </si>
+  <si>
+    <t>2 - 4</t>
+  </si>
+  <si>
+    <t>99120001114</t>
+  </si>
+  <si>
     <t>99120001117</t>
   </si>
   <si>
-    <t>99120001118</t>
-  </si>
-  <si>
-    <t>99120001114</t>
-  </si>
-  <si>
     <t>99120001120</t>
   </si>
   <si>
@@ -773,15 +776,15 @@
     <t>99120001146</t>
   </si>
   <si>
+    <t>99120001149</t>
+  </si>
+  <si>
+    <t>99120001150</t>
+  </si>
+  <si>
     <t>99120001148</t>
   </si>
   <si>
-    <t>99120001149</t>
-  </si>
-  <si>
-    <t>99120001150</t>
-  </si>
-  <si>
     <t>99120001147</t>
   </si>
   <si>
@@ -830,12 +833,12 @@
     <t>99120001167</t>
   </si>
   <si>
+    <t>99120001163</t>
+  </si>
+  <si>
     <t>99120001161</t>
   </si>
   <si>
-    <t>99120001163</t>
-  </si>
-  <si>
     <t>99120001162</t>
   </si>
   <si>
@@ -854,15 +857,15 @@
     <t>99120001176</t>
   </si>
   <si>
+    <t>99120001174</t>
+  </si>
+  <si>
+    <t>99120001175</t>
+  </si>
+  <si>
     <t>99120001172</t>
   </si>
   <si>
-    <t>99120001174</t>
-  </si>
-  <si>
-    <t>99120001175</t>
-  </si>
-  <si>
     <t>99120001169</t>
   </si>
   <si>
@@ -884,15 +887,15 @@
     <t>99120001179</t>
   </si>
   <si>
+    <t>99120001183</t>
+  </si>
+  <si>
+    <t>99120001184</t>
+  </si>
+  <si>
     <t>99120001182</t>
   </si>
   <si>
-    <t>99120001183</t>
-  </si>
-  <si>
-    <t>99120001184</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
@@ -911,15 +914,15 @@
     <t>99120001187</t>
   </si>
   <si>
+    <t>99120001190</t>
+  </si>
+  <si>
+    <t>99120001191</t>
+  </si>
+  <si>
     <t>99120001188</t>
   </si>
   <si>
-    <t>99120001190</t>
-  </si>
-  <si>
-    <t>99120001191</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
@@ -953,12 +956,12 @@
     <t>99120001205</t>
   </si>
   <si>
+    <t>99120001208</t>
+  </si>
+  <si>
     <t>99120001206</t>
   </si>
   <si>
-    <t>99120001208</t>
-  </si>
-  <si>
     <t>99120001201</t>
   </si>
   <si>
@@ -980,15 +983,15 @@
     <t>99120001209</t>
   </si>
   <si>
+    <t>99120001213</t>
+  </si>
+  <si>
+    <t>99120001214</t>
+  </si>
+  <si>
     <t>99120001211</t>
   </si>
   <si>
-    <t>99120001213</t>
-  </si>
-  <si>
-    <t>99120001214</t>
-  </si>
-  <si>
     <t>99120001210</t>
   </si>
   <si>
@@ -1010,12 +1013,12 @@
     <t>99120001221</t>
   </si>
   <si>
+    <t>99120001223</t>
+  </si>
+  <si>
     <t>99120001222</t>
   </si>
   <si>
-    <t>99120001223</t>
-  </si>
-  <si>
     <t>99120001217</t>
   </si>
   <si>
@@ -1034,25 +1037,25 @@
     <t>99120001232</t>
   </si>
   <si>
+    <t>99120001226</t>
+  </si>
+  <si>
+    <t>99120001227</t>
+  </si>
+  <si>
+    <t>99120001228</t>
+  </si>
+  <si>
+    <t>99120001229</t>
+  </si>
+  <si>
+    <t>99120001230</t>
+  </si>
+  <si>
+    <t>99120001231</t>
+  </si>
+  <si>
     <t>99120001225</t>
-  </si>
-  <si>
-    <t>99120001226</t>
-  </si>
-  <si>
-    <t>99120001227</t>
-  </si>
-  <si>
-    <t>99120001228</t>
-  </si>
-  <si>
-    <t>99120001229</t>
-  </si>
-  <si>
-    <t>99120001230</t>
-  </si>
-  <si>
-    <t>99120001231</t>
   </si>
   <si>
     <t>30</t>
@@ -1496,7 +1499,7 @@
         <v>58</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H10" s="0" t="s">
         <v>63</v>
@@ -1566,7 +1569,7 @@
         <v>68</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H12" s="0" t="s">
         <v>69</v>
@@ -1630,22 +1633,22 @@
         <v>34</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I14" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K14" s="0" t="s">
         <v>20</v>
@@ -1665,13 +1668,13 @@
         <v>34</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H15" s="0" t="s">
         <v>77</v>
@@ -1700,10 +1703,10 @@
         <v>56</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>29</v>
@@ -1770,7 +1773,7 @@
         <v>28</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>86</v>
@@ -1779,7 +1782,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I18" s="0" t="s">
         <v>18</v>
@@ -1916,7 +1919,7 @@
         <v>86</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>25</v>
@@ -1983,10 +1986,10 @@
         <v>35</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H24" s="0" t="s">
         <v>37</v>
@@ -2015,7 +2018,7 @@
         <v>56</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>97</v>
@@ -2024,7 +2027,7 @@
         <v>52</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>18</v>
@@ -2050,7 +2053,7 @@
         <v>100</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>71</v>
@@ -2231,7 +2234,7 @@
         <v>58</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>72</v>
@@ -2260,7 +2263,7 @@
         <v>34</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F32" s="0" t="s">
         <v>108</v>
@@ -2269,7 +2272,7 @@
         <v>35</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I32" s="0" t="s">
         <v>18</v>
@@ -2301,10 +2304,10 @@
         <v>86</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>18</v>
@@ -2336,7 +2339,7 @@
         <v>81</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H34" s="0" t="s">
         <v>82</v>
@@ -2365,7 +2368,7 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F35" s="0" t="s">
         <v>113</v>
@@ -2374,7 +2377,7 @@
         <v>24</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I35" s="0" t="s">
         <v>18</v>
@@ -2435,16 +2438,16 @@
         <v>28</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I37" s="0" t="s">
         <v>18</v>
@@ -2613,7 +2616,7 @@
         <v>52</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>16</v>
@@ -2686,7 +2689,7 @@
         <v>124</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H44" s="0" t="s">
         <v>25</v>
@@ -2715,16 +2718,16 @@
         <v>34</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I45" s="0" t="s">
         <v>18</v>
@@ -2750,16 +2753,16 @@
         <v>34</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="I46" s="0" t="s">
         <v>18</v>
@@ -2823,7 +2826,7 @@
         <v>35</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>57</v>
@@ -2855,7 +2858,7 @@
         <v>49</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>68</v>
@@ -2934,7 +2937,7 @@
         <v>52</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I51" s="0" t="s">
         <v>18</v>
@@ -2960,7 +2963,7 @@
         <v>28</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F52" s="0" t="s">
         <v>51</v>
@@ -3030,16 +3033,16 @@
         <v>34</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="I54" s="0" t="s">
         <v>18</v>
@@ -3065,16 +3068,16 @@
         <v>34</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="I55" s="0" t="s">
         <v>18</v>
@@ -3100,7 +3103,7 @@
         <v>49</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F56" s="0" t="s">
         <v>108</v>
@@ -3109,7 +3112,7 @@
         <v>35</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I56" s="0" t="s">
         <v>18</v>
@@ -3173,10 +3176,10 @@
         <v>14</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H58" s="0" t="s">
         <v>17</v>
@@ -3246,7 +3249,7 @@
         <v>23</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H60" s="0" t="s">
         <v>69</v>
@@ -3275,16 +3278,16 @@
         <v>34</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="I61" s="0" t="s">
         <v>18</v>
@@ -3310,16 +3313,16 @@
         <v>34</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F62" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I62" s="0" t="s">
         <v>18</v>
@@ -3415,7 +3418,7 @@
         <v>150</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>15</v>
@@ -3424,7 +3427,7 @@
         <v>31</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I65" s="0" t="s">
         <v>18</v>
@@ -3459,7 +3462,7 @@
         <v>35</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I66" s="0" t="s">
         <v>18</v>
@@ -3485,16 +3488,16 @@
         <v>13</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="I67" s="0" t="s">
         <v>18</v>
@@ -3520,16 +3523,16 @@
         <v>13</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I68" s="0" t="s">
         <v>18</v>
@@ -3590,22 +3593,22 @@
         <v>13</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F70" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H70" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="I70" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="0" t="s">
         <v>157</v>
-      </c>
-      <c r="G70" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H70" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="I70" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="0" t="s">
-        <v>158</v>
       </c>
       <c r="K70" s="0" t="s">
         <v>20</v>
@@ -3625,16 +3628,16 @@
         <v>13</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="I71" s="0" t="s">
         <v>18</v>
@@ -3695,7 +3698,7 @@
         <v>150</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>30</v>
@@ -3704,7 +3707,7 @@
         <v>57</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I73" s="0" t="s">
         <v>18</v>
@@ -3768,7 +3771,7 @@
         <v>29</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>16</v>
@@ -3806,7 +3809,7 @@
         <v>23</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H76" s="0" t="s">
         <v>63</v>
@@ -3841,7 +3844,7 @@
         <v>23</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H77" s="0" t="s">
         <v>17</v>
@@ -3905,16 +3908,16 @@
         <v>34</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>18</v>
@@ -3940,16 +3943,16 @@
         <v>34</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I80" s="0" t="s">
         <v>18</v>
@@ -3975,7 +3978,7 @@
         <v>49</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F81" s="0" t="s">
         <v>58</v>
@@ -3984,7 +3987,7 @@
         <v>52</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I81" s="0" t="s">
         <v>18</v>
@@ -4013,13 +4016,13 @@
         <v>31</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>57</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I82" s="0" t="s">
         <v>18</v>
@@ -4045,7 +4048,7 @@
         <v>56</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F83" s="0" t="s">
         <v>71</v>
@@ -4054,7 +4057,7 @@
         <v>29</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I83" s="0" t="s">
         <v>18</v>
@@ -4185,7 +4188,7 @@
         <v>56</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F87" s="0" t="s">
         <v>108</v>
@@ -4194,7 +4197,7 @@
         <v>14</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I87" s="0" t="s">
         <v>18</v>
@@ -4226,7 +4229,7 @@
         <v>15</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H88" s="0" t="s">
         <v>25</v>
@@ -4255,10 +4258,10 @@
         <v>56</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>16</v>
@@ -4325,7 +4328,7 @@
         <v>34</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F91" s="0" t="s">
         <v>181</v>
@@ -4360,16 +4363,16 @@
         <v>34</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F92" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I92" s="0" t="s">
         <v>18</v>
@@ -4395,16 +4398,16 @@
         <v>34</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F93" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I93" s="0" t="s">
         <v>18</v>
@@ -4436,7 +4439,7 @@
         <v>181</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H94" s="0" t="s">
         <v>82</v>
@@ -4541,7 +4544,7 @@
         <v>181</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H97" s="0" t="s">
         <v>60</v>
@@ -4576,7 +4579,7 @@
         <v>68</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H98" s="0" t="s">
         <v>72</v>
@@ -4605,7 +4608,7 @@
         <v>13</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F99" s="0" t="s">
         <v>108</v>
@@ -4614,7 +4617,7 @@
         <v>22</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I99" s="0" t="s">
         <v>18</v>
@@ -4646,7 +4649,7 @@
         <v>51</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H100" s="0" t="s">
         <v>53</v>
@@ -4719,7 +4722,7 @@
         <v>36</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I102" s="0" t="s">
         <v>18</v>
@@ -4745,7 +4748,7 @@
         <v>34</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F103" s="0" t="s">
         <v>108</v>
@@ -4754,7 +4757,7 @@
         <v>14</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>18</v>
@@ -4818,7 +4821,7 @@
         <v>57</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>16</v>
@@ -4850,16 +4853,16 @@
         <v>56</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F106" s="0" t="s">
         <v>201</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I106" s="0" t="s">
         <v>18</v>
@@ -4888,7 +4891,7 @@
         <v>59</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>52</v>
@@ -4955,7 +4958,7 @@
         <v>13</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F109" s="0" t="s">
         <v>15</v>
@@ -5063,7 +5066,7 @@
         <v>22</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>31</v>
@@ -5101,7 +5104,7 @@
         <v>15</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H113" s="0" t="s">
         <v>66</v>
@@ -5136,7 +5139,7 @@
         <v>113</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H114" s="0" t="s">
         <v>53</v>
@@ -5168,7 +5171,7 @@
         <v>29</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>36</v>
@@ -5203,13 +5206,13 @@
         <v>31</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>181</v>
+        <v>97</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I116" s="0" t="s">
         <v>18</v>
@@ -5235,16 +5238,16 @@
         <v>34</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="I117" s="0" t="s">
         <v>18</v>
@@ -5270,22 +5273,22 @@
         <v>34</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="I118" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J118" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K118" s="0" t="s">
         <v>20</v>
@@ -5305,22 +5308,22 @@
         <v>34</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J119" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K119" s="0" t="s">
         <v>20</v>
@@ -5340,22 +5343,22 @@
         <v>49</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I120" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J120" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K120" s="0" t="s">
         <v>20</v>
@@ -5390,7 +5393,7 @@
         <v>18</v>
       </c>
       <c r="J121" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K121" s="0" t="s">
         <v>20</v>
@@ -5398,7 +5401,7 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B122" s="2">
         <v>46234.791666666664</v>
@@ -5410,7 +5413,7 @@
         <v>56</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F122" s="0" t="s">
         <v>181</v>
@@ -5419,13 +5422,13 @@
         <v>14</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I122" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J122" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K122" s="0" t="s">
         <v>20</v>
@@ -5433,7 +5436,7 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B123" s="2">
         <v>46234.875</v>
@@ -5442,7 +5445,7 @@
         <v>132</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E123" s="0" t="s">
         <v>59</v>
@@ -5451,7 +5454,7 @@
         <v>181</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H123" s="0" t="s">
         <v>82</v>
@@ -5460,7 +5463,7 @@
         <v>18</v>
       </c>
       <c r="J123" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K123" s="0" t="s">
         <v>20</v>
@@ -5468,7 +5471,7 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B124" s="2">
         <v>46235.666666666664</v>
@@ -5486,7 +5489,7 @@
         <v>181</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H124" s="0" t="s">
         <v>72</v>
@@ -5495,7 +5498,7 @@
         <v>18</v>
       </c>
       <c r="J124" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K124" s="0" t="s">
         <v>20</v>
@@ -5503,7 +5506,7 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B125" s="2">
         <v>46235.75</v>
@@ -5530,7 +5533,7 @@
         <v>18</v>
       </c>
       <c r="J125" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K125" s="0" t="s">
         <v>20</v>
@@ -5538,7 +5541,7 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B126" s="2">
         <v>46236.708333333336</v>
@@ -5565,7 +5568,7 @@
         <v>18</v>
       </c>
       <c r="J126" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K126" s="0" t="s">
         <v>20</v>
@@ -5573,7 +5576,7 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B127" s="2">
         <v>46236.708333333336</v>
@@ -5600,7 +5603,7 @@
         <v>18</v>
       </c>
       <c r="J127" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K127" s="0" t="s">
         <v>20</v>
@@ -5608,7 +5611,7 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B128" s="2">
         <v>46236.708333333336</v>
@@ -5620,7 +5623,7 @@
         <v>34</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F128" s="0" t="s">
         <v>181</v>
@@ -5629,13 +5632,13 @@
         <v>50</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I128" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J128" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K128" s="0" t="s">
         <v>20</v>
@@ -5643,7 +5646,7 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B129" s="2">
         <v>46236.802083333336</v>
@@ -5664,13 +5667,13 @@
         <v>24</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I129" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J129" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K129" s="0" t="s">
         <v>20</v>
@@ -5678,7 +5681,7 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B130" s="2">
         <v>46141.791666666664</v>
@@ -5693,7 +5696,7 @@
         <v>50</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>31</v>
@@ -5705,7 +5708,7 @@
         <v>18</v>
       </c>
       <c r="J130" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K130" s="0" t="s">
         <v>20</v>
@@ -5713,7 +5716,7 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B131" s="2">
         <v>46241.791666666664</v>
@@ -5725,7 +5728,7 @@
         <v>56</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>181</v>
@@ -5734,13 +5737,13 @@
         <v>35</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I131" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J131" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K131" s="0" t="s">
         <v>20</v>
@@ -5748,7 +5751,7 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B132" s="2">
         <v>46242.583333333336</v>
@@ -5760,7 +5763,7 @@
         <v>100</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F132" s="0" t="s">
         <v>181</v>
@@ -5769,13 +5772,13 @@
         <v>59</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I132" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J132" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K132" s="0" t="s">
         <v>20</v>
@@ -5783,7 +5786,7 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B133" s="2">
         <v>46242.666666666664</v>
@@ -5810,7 +5813,7 @@
         <v>18</v>
       </c>
       <c r="J133" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K133" s="0" t="s">
         <v>20</v>
@@ -5818,7 +5821,7 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B134" s="2">
         <v>46242.75</v>
@@ -5845,7 +5848,7 @@
         <v>18</v>
       </c>
       <c r="J134" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K134" s="0" t="s">
         <v>20</v>
@@ -5853,7 +5856,7 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B135" s="2">
         <v>46243.604166666664</v>
@@ -5865,7 +5868,7 @@
         <v>28</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F135" s="0" t="s">
         <v>181</v>
@@ -5880,7 +5883,7 @@
         <v>18</v>
       </c>
       <c r="J135" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K135" s="0" t="s">
         <v>20</v>
@@ -5888,7 +5891,7 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B136" s="2">
         <v>46243.708333333336</v>
@@ -5906,7 +5909,7 @@
         <v>181</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H136" s="0" t="s">
         <v>17</v>
@@ -5915,7 +5918,7 @@
         <v>18</v>
       </c>
       <c r="J136" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K136" s="0" t="s">
         <v>20</v>
@@ -5923,7 +5926,7 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B137" s="2">
         <v>46243.802083333336</v>
@@ -5950,7 +5953,7 @@
         <v>18</v>
       </c>
       <c r="J137" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K137" s="0" t="s">
         <v>20</v>
@@ -5958,7 +5961,7 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B138" s="2">
         <v>46142.791666666664</v>
@@ -5985,7 +5988,7 @@
         <v>18</v>
       </c>
       <c r="J138" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K138" s="0" t="s">
         <v>20</v>
@@ -5993,7 +5996,7 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B139" s="2">
         <v>46248.791666666664</v>
@@ -6020,7 +6023,7 @@
         <v>18</v>
       </c>
       <c r="J139" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K139" s="0" t="s">
         <v>20</v>
@@ -6028,7 +6031,7 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B140" s="2">
         <v>46249.666666666664</v>
@@ -6046,7 +6049,7 @@
         <v>181</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H140" s="0" t="s">
         <v>37</v>
@@ -6055,7 +6058,7 @@
         <v>18</v>
       </c>
       <c r="J140" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K140" s="0" t="s">
         <v>20</v>
@@ -6063,7 +6066,7 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B141" s="2">
         <v>46250.604166666664</v>
@@ -6075,22 +6078,22 @@
         <v>28</v>
       </c>
       <c r="E141" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F141" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="G141" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="G141" s="0" t="s">
-        <v>39</v>
-      </c>
       <c r="H141" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I141" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J141" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K141" s="0" t="s">
         <v>20</v>
@@ -6098,7 +6101,7 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B142" s="2">
         <v>46250.708333333336</v>
@@ -6125,7 +6128,7 @@
         <v>18</v>
       </c>
       <c r="J142" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K142" s="0" t="s">
         <v>20</v>
@@ -6133,7 +6136,7 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B143" s="2">
         <v>46250.708333333336</v>
@@ -6151,7 +6154,7 @@
         <v>181</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H143" s="0" t="s">
         <v>60</v>
@@ -6160,7 +6163,7 @@
         <v>18</v>
       </c>
       <c r="J143" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K143" s="0" t="s">
         <v>20</v>
@@ -6168,7 +6171,7 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B144" s="2">
         <v>46250.708333333336</v>
@@ -6189,13 +6192,13 @@
         <v>14</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I144" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J144" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K144" s="0" t="s">
         <v>20</v>
@@ -6203,7 +6206,7 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B145" s="2">
         <v>46250.802083333336</v>
@@ -6230,7 +6233,7 @@
         <v>18</v>
       </c>
       <c r="J145" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K145" s="0" t="s">
         <v>20</v>
@@ -6238,7 +6241,7 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B146" s="2">
         <v>46263.666666666664</v>
@@ -6250,7 +6253,7 @@
         <v>13</v>
       </c>
       <c r="E146" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F146" s="0" t="s">
         <v>181</v>
@@ -6259,13 +6262,13 @@
         <v>22</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J146" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K146" s="0" t="s">
         <v>20</v>
@@ -6273,7 +6276,7 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B147" s="2">
         <v>46263.75</v>
@@ -6291,7 +6294,7 @@
         <v>181</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H147" s="0" t="s">
         <v>66</v>
@@ -6300,7 +6303,7 @@
         <v>18</v>
       </c>
       <c r="J147" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K147" s="0" t="s">
         <v>20</v>
@@ -6308,7 +6311,7 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B148" s="2">
         <v>46264.604166666664</v>
@@ -6335,7 +6338,7 @@
         <v>18</v>
       </c>
       <c r="J148" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K148" s="0" t="s">
         <v>20</v>
@@ -6343,7 +6346,7 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B149" s="2">
         <v>46264.708333333336</v>
@@ -6370,7 +6373,7 @@
         <v>18</v>
       </c>
       <c r="J149" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K149" s="0" t="s">
         <v>20</v>
@@ -6378,7 +6381,7 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B150" s="2">
         <v>46264.708333333336</v>
@@ -6390,22 +6393,22 @@
         <v>34</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F150" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="I150" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J150" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K150" s="0" t="s">
         <v>20</v>
@@ -6413,7 +6416,7 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B151" s="2">
         <v>46264.708333333336</v>
@@ -6425,22 +6428,22 @@
         <v>34</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F151" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I151" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J151" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K151" s="0" t="s">
         <v>20</v>
@@ -6448,7 +6451,7 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B152" s="2">
         <v>46264.708333333336</v>
@@ -6460,22 +6463,22 @@
         <v>34</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F152" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I152" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J152" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K152" s="0" t="s">
         <v>20</v>
@@ -6483,7 +6486,7 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B153" s="2">
         <v>46264.802083333336</v>
@@ -6495,7 +6498,7 @@
         <v>49</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F153" s="0" t="s">
         <v>181</v>
@@ -6510,7 +6513,7 @@
         <v>18</v>
       </c>
       <c r="J153" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K153" s="0" t="s">
         <v>20</v>
@@ -6518,7 +6521,7 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B154" s="2">
         <v>46269.791666666664</v>
@@ -6545,7 +6548,7 @@
         <v>18</v>
       </c>
       <c r="J154" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K154" s="0" t="s">
         <v>20</v>
@@ -6553,7 +6556,7 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B155" s="2">
         <v>46269.791666666664</v>
@@ -6565,7 +6568,7 @@
         <v>56</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F155" s="0" t="s">
         <v>181</v>
@@ -6574,13 +6577,13 @@
         <v>36</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I155" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J155" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K155" s="0" t="s">
         <v>20</v>
@@ -6588,7 +6591,7 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B156" s="2">
         <v>46269.875</v>
@@ -6597,10 +6600,10 @@
         <v>132</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E156" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F156" s="0" t="s">
         <v>181</v>
@@ -6609,13 +6612,13 @@
         <v>16</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J156" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K156" s="0" t="s">
         <v>20</v>
@@ -6623,7 +6626,7 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B157" s="2">
         <v>46270.666666666664</v>
@@ -6650,7 +6653,7 @@
         <v>18</v>
       </c>
       <c r="J157" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K157" s="0" t="s">
         <v>20</v>
@@ -6658,7 +6661,7 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B158" s="2">
         <v>46270.75</v>
@@ -6676,16 +6679,16 @@
         <v>181</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I158" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J158" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K158" s="0" t="s">
         <v>20</v>
@@ -6693,7 +6696,7 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B159" s="2">
         <v>46271.708333333336</v>
@@ -6720,7 +6723,7 @@
         <v>18</v>
       </c>
       <c r="J159" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K159" s="0" t="s">
         <v>20</v>
@@ -6728,7 +6731,7 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B160" s="2">
         <v>46271.802083333336</v>
@@ -6755,7 +6758,7 @@
         <v>18</v>
       </c>
       <c r="J160" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K160" s="0" t="s">
         <v>20</v>
@@ -6763,7 +6766,7 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B161" s="2">
         <v>46272.791666666664</v>
@@ -6781,7 +6784,7 @@
         <v>181</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H161" s="0" t="s">
         <v>60</v>
@@ -6790,7 +6793,7 @@
         <v>18</v>
       </c>
       <c r="J161" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K161" s="0" t="s">
         <v>20</v>
@@ -6798,7 +6801,7 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B162" s="2">
         <v>46277.666666666664</v>
@@ -6810,13 +6813,13 @@
         <v>13</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F162" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H162" s="0" t="s">
         <v>79</v>
@@ -6825,7 +6828,7 @@
         <v>18</v>
       </c>
       <c r="J162" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K162" s="0" t="s">
         <v>20</v>
@@ -6833,7 +6836,7 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B163" s="2">
         <v>46277.75</v>
@@ -6860,7 +6863,7 @@
         <v>18</v>
       </c>
       <c r="J163" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K163" s="0" t="s">
         <v>20</v>
@@ -6868,7 +6871,7 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B164" s="2">
         <v>46278.604166666664</v>
@@ -6895,7 +6898,7 @@
         <v>18</v>
       </c>
       <c r="J164" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K164" s="0" t="s">
         <v>20</v>
@@ -6903,7 +6906,7 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B165" s="2">
         <v>46278.708333333336</v>
@@ -6921,7 +6924,7 @@
         <v>181</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H165" s="0" t="s">
         <v>37</v>
@@ -6930,7 +6933,7 @@
         <v>18</v>
       </c>
       <c r="J165" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K165" s="0" t="s">
         <v>20</v>
@@ -6938,7 +6941,7 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B166" s="2">
         <v>46278.708333333336</v>
@@ -6965,7 +6968,7 @@
         <v>18</v>
       </c>
       <c r="J166" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K166" s="0" t="s">
         <v>20</v>
@@ -6973,7 +6976,7 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B167" s="2">
         <v>46278.708333333336</v>
@@ -6985,22 +6988,22 @@
         <v>34</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="F167" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I167" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J167" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K167" s="0" t="s">
         <v>20</v>
@@ -7008,7 +7011,7 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B168" s="2">
         <v>46278.708333333336</v>
@@ -7020,22 +7023,22 @@
         <v>34</v>
       </c>
       <c r="E168" s="0" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="F168" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="I168" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J168" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K168" s="0" t="s">
         <v>20</v>
@@ -7043,7 +7046,7 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B169" s="2">
         <v>46278.802083333336</v>
@@ -7070,7 +7073,7 @@
         <v>18</v>
       </c>
       <c r="J169" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K169" s="0" t="s">
         <v>20</v>
@@ -7078,7 +7081,7 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B170" s="2">
         <v>46283.791666666664</v>
@@ -7105,7 +7108,7 @@
         <v>18</v>
       </c>
       <c r="J170" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K170" s="0" t="s">
         <v>20</v>
@@ -7113,7 +7116,7 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B171" s="2">
         <v>46284.666666666664</v>
@@ -7140,7 +7143,7 @@
         <v>18</v>
       </c>
       <c r="J171" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K171" s="0" t="s">
         <v>20</v>
@@ -7148,7 +7151,7 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B172" s="2">
         <v>46284.75</v>
@@ -7166,7 +7169,7 @@
         <v>181</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H172" s="0" t="s">
         <v>25</v>
@@ -7175,7 +7178,7 @@
         <v>18</v>
       </c>
       <c r="J172" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K172" s="0" t="s">
         <v>20</v>
@@ -7183,7 +7186,7 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B173" s="2">
         <v>46285.604166666664</v>
@@ -7195,7 +7198,7 @@
         <v>28</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F173" s="0" t="s">
         <v>181</v>
@@ -7204,13 +7207,13 @@
         <v>52</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I173" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J173" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K173" s="0" t="s">
         <v>20</v>
@@ -7218,7 +7221,7 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B174" s="2">
         <v>46285.708333333336</v>
@@ -7230,22 +7233,22 @@
         <v>34</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F174" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="I174" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J174" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K174" s="0" t="s">
         <v>20</v>
@@ -7253,7 +7256,7 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B175" s="2">
         <v>46285.708333333336</v>
@@ -7265,22 +7268,22 @@
         <v>34</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F175" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I175" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J175" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K175" s="0" t="s">
         <v>20</v>
@@ -7288,7 +7291,7 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B176" s="2">
         <v>46285.708333333336</v>
@@ -7300,22 +7303,22 @@
         <v>34</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F176" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I176" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J176" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K176" s="0" t="s">
         <v>20</v>
@@ -7323,7 +7326,7 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B177" s="2">
         <v>46285.802083333336</v>
@@ -7344,13 +7347,13 @@
         <v>59</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I177" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J177" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K177" s="0" t="s">
         <v>20</v>
@@ -7358,7 +7361,7 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B178" s="2">
         <v>46306.708333333336</v>
@@ -7376,7 +7379,7 @@
         <v>181</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H178" s="0" t="s">
         <v>37</v>
@@ -7385,7 +7388,7 @@
         <v>18</v>
       </c>
       <c r="J178" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K178" s="0" t="s">
         <v>20</v>
@@ -7393,7 +7396,7 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B179" s="2">
         <v>46306.708333333336</v>
@@ -7405,7 +7408,7 @@
         <v>34</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F179" s="0" t="s">
         <v>181</v>
@@ -7420,7 +7423,7 @@
         <v>18</v>
       </c>
       <c r="J179" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K179" s="0" t="s">
         <v>20</v>
@@ -7428,7 +7431,7 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B180" s="2">
         <v>46306.708333333336</v>
@@ -7455,7 +7458,7 @@
         <v>18</v>
       </c>
       <c r="J180" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K180" s="0" t="s">
         <v>20</v>
@@ -7463,7 +7466,7 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B181" s="2">
         <v>46306.708333333336</v>
@@ -7484,13 +7487,13 @@
         <v>16</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J181" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K181" s="0" t="s">
         <v>20</v>
@@ -7498,7 +7501,7 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B182" s="2">
         <v>46306.708333333336</v>
@@ -7525,7 +7528,7 @@
         <v>18</v>
       </c>
       <c r="J182" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K182" s="0" t="s">
         <v>20</v>
@@ -7533,7 +7536,7 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B183" s="2">
         <v>46306.708333333336</v>
@@ -7545,22 +7548,22 @@
         <v>34</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G183" s="0" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I183" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J183" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K183" s="0" t="s">
         <v>20</v>
@@ -7568,7 +7571,7 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B184" s="2">
         <v>46306.708333333336</v>
@@ -7580,22 +7583,22 @@
         <v>34</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F184" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G184" s="0" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="I184" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J184" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K184" s="0" t="s">
         <v>20</v>
@@ -7603,7 +7606,7 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B185" s="2">
         <v>46306.708333333336</v>
@@ -7615,22 +7618,22 @@
         <v>34</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="I185" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J185" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K185" s="0" t="s">
         <v>20</v>
@@ -7638,7 +7641,7 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B186" s="2">
         <v>46313.708333333336</v>
@@ -7656,7 +7659,7 @@
         <v>181</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H186" s="0" t="s">
         <v>32</v>
@@ -7665,7 +7668,7 @@
         <v>18</v>
       </c>
       <c r="J186" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K186" s="0" t="s">
         <v>20</v>
@@ -7673,7 +7676,7 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B187" s="2">
         <v>46313.708333333336</v>
@@ -7700,7 +7703,7 @@
         <v>18</v>
       </c>
       <c r="J187" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K187" s="0" t="s">
         <v>20</v>
@@ -7708,7 +7711,7 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B188" s="2">
         <v>46313.708333333336</v>
@@ -7720,7 +7723,7 @@
         <v>34</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F188" s="0" t="s">
         <v>181</v>
@@ -7729,13 +7732,13 @@
         <v>31</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I188" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J188" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K188" s="0" t="s">
         <v>20</v>
@@ -7743,7 +7746,7 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B189" s="2">
         <v>46313.708333333336</v>
@@ -7770,7 +7773,7 @@
         <v>18</v>
       </c>
       <c r="J189" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K189" s="0" t="s">
         <v>20</v>
@@ -7778,7 +7781,7 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B190" s="2">
         <v>46313.708333333336</v>
@@ -7805,7 +7808,7 @@
         <v>18</v>
       </c>
       <c r="J190" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K190" s="0" t="s">
         <v>20</v>
@@ -7813,7 +7816,7 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B191" s="2">
         <v>46313.708333333336</v>
@@ -7825,22 +7828,22 @@
         <v>34</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F191" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G191" s="0" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="I191" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J191" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K191" s="0" t="s">
         <v>20</v>
@@ -7848,7 +7851,7 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B192" s="2">
         <v>46313.708333333336</v>
@@ -7860,22 +7863,22 @@
         <v>34</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F192" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J192" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K192" s="0" t="s">
         <v>20</v>
@@ -7883,7 +7886,7 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B193" s="2">
         <v>46313.708333333336</v>
@@ -7895,22 +7898,22 @@
         <v>34</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F193" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G193" s="0" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I193" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J193" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K193" s="0" t="s">
         <v>20</v>
@@ -7918,7 +7921,7 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B194" s="2">
         <v>46327.708333333336</v>
@@ -7945,7 +7948,7 @@
         <v>18</v>
       </c>
       <c r="J194" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K194" s="0" t="s">
         <v>20</v>
@@ -7953,7 +7956,7 @@
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B195" s="2">
         <v>46327.708333333336</v>
@@ -7965,7 +7968,7 @@
         <v>34</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>181</v>
@@ -7974,13 +7977,13 @@
         <v>50</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J195" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K195" s="0" t="s">
         <v>20</v>
@@ -7988,7 +7991,7 @@
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B196" s="2">
         <v>46327.708333333336</v>
@@ -8015,7 +8018,7 @@
         <v>18</v>
       </c>
       <c r="J196" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K196" s="0" t="s">
         <v>20</v>
@@ -8023,7 +8026,7 @@
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B197" s="2">
         <v>46327.708333333336</v>
@@ -8044,13 +8047,13 @@
         <v>22</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J197" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K197" s="0" t="s">
         <v>20</v>
@@ -8058,7 +8061,7 @@
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B198" s="2">
         <v>46327.708333333336</v>
@@ -8085,7 +8088,7 @@
         <v>18</v>
       </c>
       <c r="J198" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K198" s="0" t="s">
         <v>20</v>
@@ -8093,7 +8096,7 @@
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B199" s="2">
         <v>46327.708333333336</v>
@@ -8120,7 +8123,7 @@
         <v>18</v>
       </c>
       <c r="J199" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K199" s="0" t="s">
         <v>20</v>
@@ -8128,7 +8131,7 @@
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B200" s="2">
         <v>46327.708333333336</v>
@@ -8146,7 +8149,7 @@
         <v>181</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H200" s="0" t="s">
         <v>63</v>
@@ -8155,7 +8158,7 @@
         <v>18</v>
       </c>
       <c r="J200" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K200" s="0" t="s">
         <v>20</v>
@@ -8163,7 +8166,7 @@
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B201" s="2">
         <v>46327.708333333336</v>
@@ -8175,22 +8178,22 @@
         <v>34</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F201" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I201" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J201" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K201" s="0" t="s">
         <v>20</v>
@@ -8198,7 +8201,7 @@
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B202" s="2">
         <v>46334.708333333336</v>
@@ -8225,7 +8228,7 @@
         <v>18</v>
       </c>
       <c r="J202" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K202" s="0" t="s">
         <v>20</v>
@@ -8233,7 +8236,7 @@
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B203" s="2">
         <v>46334.708333333336</v>
@@ -8245,22 +8248,22 @@
         <v>34</v>
       </c>
       <c r="E203" s="0" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="F203" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G203" s="0" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I203" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J203" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K203" s="0" t="s">
         <v>20</v>
@@ -8268,7 +8271,7 @@
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B204" s="2">
         <v>46334.708333333336</v>
@@ -8280,22 +8283,22 @@
         <v>34</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F204" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G204" s="0" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I204" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J204" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K204" s="0" t="s">
         <v>20</v>
@@ -8303,7 +8306,7 @@
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B205" s="2">
         <v>46334.708333333336</v>
@@ -8330,7 +8333,7 @@
         <v>18</v>
       </c>
       <c r="J205" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K205" s="0" t="s">
         <v>20</v>
@@ -8338,7 +8341,7 @@
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B206" s="2">
         <v>46334.708333333336</v>
@@ -8365,7 +8368,7 @@
         <v>18</v>
       </c>
       <c r="J206" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K206" s="0" t="s">
         <v>20</v>
@@ -8373,7 +8376,7 @@
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B207" s="2">
         <v>46334.708333333336</v>
@@ -8391,7 +8394,7 @@
         <v>181</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H207" s="0" t="s">
         <v>32</v>
@@ -8400,7 +8403,7 @@
         <v>18</v>
       </c>
       <c r="J207" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K207" s="0" t="s">
         <v>20</v>
@@ -8408,7 +8411,7 @@
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B208" s="2">
         <v>46334.708333333336</v>
@@ -8420,13 +8423,13 @@
         <v>34</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F208" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H208" s="0" t="s">
         <v>79</v>
@@ -8435,7 +8438,7 @@
         <v>18</v>
       </c>
       <c r="J208" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K208" s="0" t="s">
         <v>20</v>
@@ -8443,7 +8446,7 @@
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B209" s="2">
         <v>46334.708333333336</v>
@@ -8470,7 +8473,7 @@
         <v>18</v>
       </c>
       <c r="J209" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K209" s="0" t="s">
         <v>20</v>
@@ -8478,7 +8481,7 @@
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B210" s="2">
         <v>46348.708333333336</v>
@@ -8505,7 +8508,7 @@
         <v>18</v>
       </c>
       <c r="J210" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K210" s="0" t="s">
         <v>20</v>
@@ -8513,7 +8516,7 @@
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B211" s="2">
         <v>46348.708333333336</v>
@@ -8525,7 +8528,7 @@
         <v>34</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="F211" s="0" t="s">
         <v>181</v>
@@ -8534,13 +8537,13 @@
         <v>41</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="I211" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J211" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K211" s="0" t="s">
         <v>20</v>
@@ -8548,7 +8551,7 @@
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B212" s="2">
         <v>46348.708333333336</v>
@@ -8560,22 +8563,22 @@
         <v>34</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F212" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G212" s="0" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I212" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J212" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K212" s="0" t="s">
         <v>20</v>
@@ -8583,7 +8586,7 @@
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B213" s="2">
         <v>46348.708333333336</v>
@@ -8595,22 +8598,22 @@
         <v>34</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F213" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="I213" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J213" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K213" s="0" t="s">
         <v>20</v>
@@ -8618,7 +8621,7 @@
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B214" s="2">
         <v>46348.708333333336</v>
@@ -8645,7 +8648,7 @@
         <v>18</v>
       </c>
       <c r="J214" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K214" s="0" t="s">
         <v>20</v>
@@ -8653,7 +8656,7 @@
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B215" s="2">
         <v>46348.708333333336</v>
@@ -8680,7 +8683,7 @@
         <v>18</v>
       </c>
       <c r="J215" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K215" s="0" t="s">
         <v>20</v>
@@ -8688,7 +8691,7 @@
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B216" s="2">
         <v>46348.708333333336</v>
@@ -8700,7 +8703,7 @@
         <v>34</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F216" s="0" t="s">
         <v>181</v>
@@ -8709,13 +8712,13 @@
         <v>36</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I216" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J216" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K216" s="0" t="s">
         <v>20</v>
@@ -8723,7 +8726,7 @@
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B217" s="2">
         <v>46348.708333333336</v>
@@ -8735,7 +8738,7 @@
         <v>34</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F217" s="0" t="s">
         <v>181</v>
@@ -8744,13 +8747,13 @@
         <v>24</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I217" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J217" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K217" s="0" t="s">
         <v>20</v>
@@ -8758,7 +8761,7 @@
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B218" s="2">
         <v>46355.708333333336</v>
@@ -8779,13 +8782,13 @@
         <v>29</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I218" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J218" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K218" s="0" t="s">
         <v>20</v>
@@ -8793,7 +8796,7 @@
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B219" s="2">
         <v>46355.708333333336</v>
@@ -8820,7 +8823,7 @@
         <v>18</v>
       </c>
       <c r="J219" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K219" s="0" t="s">
         <v>20</v>
@@ -8828,7 +8831,7 @@
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B220" s="2">
         <v>46355.708333333336</v>
@@ -8840,22 +8843,22 @@
         <v>34</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F220" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="I220" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J220" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K220" s="0" t="s">
         <v>20</v>
@@ -8863,7 +8866,7 @@
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B221" s="2">
         <v>46355.708333333336</v>
@@ -8875,22 +8878,22 @@
         <v>34</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F221" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="I221" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J221" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K221" s="0" t="s">
         <v>20</v>
@@ -8898,7 +8901,7 @@
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B222" s="2">
         <v>46355.708333333336</v>
@@ -8925,7 +8928,7 @@
         <v>18</v>
       </c>
       <c r="J222" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K222" s="0" t="s">
         <v>20</v>
@@ -8933,7 +8936,7 @@
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B223" s="2">
         <v>46355.708333333336</v>
@@ -8951,7 +8954,7 @@
         <v>181</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H223" s="0" t="s">
         <v>72</v>
@@ -8960,7 +8963,7 @@
         <v>18</v>
       </c>
       <c r="J223" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K223" s="0" t="s">
         <v>20</v>
@@ -8968,7 +8971,7 @@
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B224" s="2">
         <v>46355.708333333336</v>
@@ -8980,7 +8983,7 @@
         <v>34</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F224" s="0" t="s">
         <v>181</v>
@@ -8995,7 +8998,7 @@
         <v>18</v>
       </c>
       <c r="J224" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K224" s="0" t="s">
         <v>20</v>
@@ -9003,7 +9006,7 @@
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B225" s="2">
         <v>46355.708333333336</v>
@@ -9021,7 +9024,7 @@
         <v>181</v>
       </c>
       <c r="G225" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H225" s="0" t="s">
         <v>66</v>
@@ -9030,7 +9033,7 @@
         <v>18</v>
       </c>
       <c r="J225" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K225" s="0" t="s">
         <v>20</v>
@@ -9038,7 +9041,7 @@
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B226" s="2">
         <v>46362.708333333336</v>
@@ -9050,7 +9053,7 @@
         <v>34</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F226" s="0" t="s">
         <v>181</v>
@@ -9059,13 +9062,13 @@
         <v>59</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I226" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J226" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K226" s="0" t="s">
         <v>20</v>
@@ -9073,7 +9076,7 @@
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B227" s="2">
         <v>46362.708333333336</v>
@@ -9085,22 +9088,22 @@
         <v>34</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F227" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G227" s="0" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I227" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J227" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K227" s="0" t="s">
         <v>20</v>
@@ -9108,7 +9111,7 @@
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B228" s="2">
         <v>46362.708333333336</v>
@@ -9120,22 +9123,22 @@
         <v>34</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F228" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I228" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J228" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K228" s="0" t="s">
         <v>20</v>
@@ -9143,7 +9146,7 @@
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B229" s="2">
         <v>46362.708333333336</v>
@@ -9155,22 +9158,22 @@
         <v>34</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F229" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I229" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J229" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K229" s="0" t="s">
         <v>20</v>
@@ -9178,7 +9181,7 @@
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B230" s="2">
         <v>46362.708333333336</v>
@@ -9190,22 +9193,22 @@
         <v>34</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="F230" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I230" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J230" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K230" s="0" t="s">
         <v>20</v>
@@ -9213,7 +9216,7 @@
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B231" s="2">
         <v>46362.708333333336</v>
@@ -9225,22 +9228,22 @@
         <v>34</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F231" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I231" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J231" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K231" s="0" t="s">
         <v>20</v>
@@ -9248,7 +9251,7 @@
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B232" s="2">
         <v>46362.708333333336</v>
@@ -9260,22 +9263,22 @@
         <v>34</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F232" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I232" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J232" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K232" s="0" t="s">
         <v>20</v>
@@ -9283,7 +9286,7 @@
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B233" s="2">
         <v>46362.708333333336</v>
@@ -9295,22 +9298,22 @@
         <v>34</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F233" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I233" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J233" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K233" s="0" t="s">
         <v>20</v>
@@ -9318,7 +9321,7 @@
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B234" s="2">
         <v>46369.708333333336</v>
@@ -9345,7 +9348,7 @@
         <v>18</v>
       </c>
       <c r="J234" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K234" s="0" t="s">
         <v>20</v>
@@ -9353,7 +9356,7 @@
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B235" s="2">
         <v>46369.708333333336</v>
@@ -9380,7 +9383,7 @@
         <v>18</v>
       </c>
       <c r="J235" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K235" s="0" t="s">
         <v>20</v>
@@ -9388,7 +9391,7 @@
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B236" s="2">
         <v>46369.708333333336</v>
@@ -9415,7 +9418,7 @@
         <v>18</v>
       </c>
       <c r="J236" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K236" s="0" t="s">
         <v>20</v>
@@ -9423,7 +9426,7 @@
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B237" s="2">
         <v>46369.708333333336</v>
@@ -9450,7 +9453,7 @@
         <v>18</v>
       </c>
       <c r="J237" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K237" s="0" t="s">
         <v>20</v>
@@ -9458,7 +9461,7 @@
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B238" s="2">
         <v>46369.708333333336</v>
@@ -9485,7 +9488,7 @@
         <v>18</v>
       </c>
       <c r="J238" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K238" s="0" t="s">
         <v>20</v>
@@ -9493,7 +9496,7 @@
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B239" s="2">
         <v>46369.708333333336</v>
@@ -9511,16 +9514,16 @@
         <v>181</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I239" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J239" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K239" s="0" t="s">
         <v>20</v>
@@ -9528,7 +9531,7 @@
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B240" s="2">
         <v>46369.708333333336</v>
@@ -9540,7 +9543,7 @@
         <v>34</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F240" s="0" t="s">
         <v>181</v>
@@ -9555,7 +9558,7 @@
         <v>18</v>
       </c>
       <c r="J240" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K240" s="0" t="s">
         <v>20</v>
@@ -9563,7 +9566,7 @@
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B241" s="2">
         <v>46369.708333333336</v>
@@ -9575,22 +9578,22 @@
         <v>34</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F241" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I241" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J241" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K241" s="0" t="s">
         <v>20</v>
